--- a/input/reg_leave_parental_home.xlsx
+++ b/input/reg_leave_parental_home.xlsx
@@ -128,7 +128,7 @@
     <t>demRgnUKN</t>
   </si>
   <si>
-    <t>demYear</t>
+    <t>demYearTransformed</t>
   </si>
   <si>
     <t>demYear2020</t>
@@ -402,13 +402,13 @@
         <v>45</v>
       </c>
       <c r="B4">
-        <v>0.068654466387274016</v>
+        <v>0.066948218154622485</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
       <c r="F4">
-        <v>679.33460442797423</v>
+        <v>690.70153573369316</v>
       </c>
     </row>
     <row r="5">
@@ -416,13 +416,13 @@
         <v>46</v>
       </c>
       <c r="B5">
-        <v>23753</v>
+        <v>24036</v>
       </c>
       <c r="E5" t="s">
         <v>48</v>
       </c>
       <c r="F5">
-        <v>-4449631.2959821643</v>
+        <v>-4580249.4323749552</v>
       </c>
     </row>
   </sheetData>
@@ -537,97 +537,97 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>-0.20318178300274065</v>
+        <v>-0.20691948628767518</v>
       </c>
       <c r="C2">
-        <v>0.0010260403871276635</v>
+        <v>0.0009941069253147708</v>
       </c>
       <c r="D2">
-        <v>-5.7942231086410229e-005</v>
+        <v>-4.9840715093806432e-005</v>
       </c>
       <c r="E2">
-        <v>7.0552449275329866e-007</v>
+        <v>5.7940684815536636e-007</v>
       </c>
       <c r="F2">
-        <v>-0.00021197938057616363</v>
+        <v>-0.00020928808830303664</v>
       </c>
       <c r="G2">
-        <v>-0.00014406465454916244</v>
+        <v>-0.00014213747318839987</v>
       </c>
       <c r="H2">
-        <v>-0.00030140793155994844</v>
+        <v>-0.00028077360736408308</v>
       </c>
       <c r="I2">
-        <v>0.00010992743708696897</v>
+        <v>0.00011693215038753348</v>
       </c>
       <c r="J2">
-        <v>-6.3586271895521706e-005</v>
+        <v>-6.8444517816496439e-005</v>
       </c>
       <c r="K2">
-        <v>-2.9641244509623939e-005</v>
+        <v>-3.6853875254175703e-005</v>
       </c>
       <c r="L2">
-        <v>-1.0368023249293773e-005</v>
+        <v>-2.2440980154536251e-005</v>
       </c>
       <c r="M2">
-        <v>6.1358318463479801e-006</v>
+        <v>-8.9092834616001046e-006</v>
       </c>
       <c r="N2">
-        <v>-6.5427681280571192e-005</v>
+        <v>-7.0962650636526443e-005</v>
       </c>
       <c r="O2">
-        <v>-0.0001540994945668651</v>
+        <v>-0.00015518119750959294</v>
       </c>
       <c r="P2">
-        <v>0.0001901710139219859</v>
+        <v>0.00016438002439312681</v>
       </c>
       <c r="Q2">
-        <v>2.4286437325781278e-005</v>
+        <v>1.0584537154877346e-005</v>
       </c>
       <c r="R2">
-        <v>1.4892058278357213e-005</v>
+        <v>1.0874507537781872e-005</v>
       </c>
       <c r="S2">
-        <v>4.6428926975511335e-005</v>
+        <v>5.9699405613395097e-005</v>
       </c>
       <c r="T2">
-        <v>-3.5958054796422462e-005</v>
+        <v>-3.1771608435001794e-005</v>
       </c>
       <c r="U2">
-        <v>-4.1301744140845342e-005</v>
+        <v>-5.1570223737230764e-005</v>
       </c>
       <c r="V2">
-        <v>3.6187792571575235e-005</v>
+        <v>4.1294202976552261e-005</v>
       </c>
       <c r="W2">
-        <v>-1.7544118655730776e-005</v>
+        <v>-1.5039910363546828e-005</v>
       </c>
       <c r="X2">
-        <v>-2.276573461783743e-005</v>
+        <v>-1.4977656740259843e-005</v>
       </c>
       <c r="Y2">
-        <v>6.5013478474758725e-005</v>
+        <v>6.0594841515417539e-005</v>
       </c>
       <c r="Z2">
-        <v>1.3427259276957812e-006</v>
+        <v>6.5302543672525151e-007</v>
       </c>
       <c r="AA2">
-        <v>3.7105333980688243e-005</v>
+        <v>4.3492316941387736e-005</v>
       </c>
       <c r="AB2">
-        <v>3.37528032464147e-005</v>
+        <v>2.1021733859948034e-005</v>
       </c>
       <c r="AC2">
-        <v>-1.9904845906785703e-005</v>
+        <v>-2.0599383813811514e-005</v>
       </c>
       <c r="AD2">
-        <v>-0.0004652718649726449</v>
+        <v>-0.00047149176486758614</v>
       </c>
       <c r="AE2">
-        <v>2.5720529073133588e-006</v>
+        <v>-2.4216010275010592e-005</v>
       </c>
       <c r="AF2">
-        <v>0.00058074083582644251</v>
+        <v>0.00049682436959361416</v>
       </c>
     </row>
     <row r="3">
@@ -635,97 +635,97 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.19234895175413907</v>
+        <v>0.19746408237471141</v>
       </c>
       <c r="C3">
-        <v>-5.7942231086410229e-005</v>
+        <v>-4.9840715093806432e-005</v>
       </c>
       <c r="D3">
-        <v>0.0011917891459240109</v>
+        <v>0.001238876308539456</v>
       </c>
       <c r="E3">
-        <v>-2.1807274708357105e-005</v>
+        <v>-2.2742201372463721e-005</v>
       </c>
       <c r="F3">
-        <v>0.00073597551318355841</v>
+        <v>0.00074785210010035403</v>
       </c>
       <c r="G3">
-        <v>0.00044698515438757174</v>
+        <v>0.00045482078467390798</v>
       </c>
       <c r="H3">
-        <v>0.00056499682685125111</v>
+        <v>0.00058322308148082568</v>
       </c>
       <c r="I3">
-        <v>0.00061373869255915408</v>
+        <v>0.00062552257235919334</v>
       </c>
       <c r="J3">
-        <v>0.00049644080088420283</v>
+        <v>0.00052269196264448066</v>
       </c>
       <c r="K3">
-        <v>0.00062217875906899498</v>
+        <v>0.00063209572422124585</v>
       </c>
       <c r="L3">
-        <v>0.00055792788299802512</v>
+        <v>0.00056749030562737966</v>
       </c>
       <c r="M3">
-        <v>0.00052508275896529725</v>
+        <v>0.00054614448249212767</v>
       </c>
       <c r="N3">
-        <v>0.00072309083467292238</v>
+        <v>0.00074007853589422171</v>
       </c>
       <c r="O3">
-        <v>0.00024806444867658817</v>
+        <v>0.00027035978605119285</v>
       </c>
       <c r="P3">
-        <v>0.0002131504825218962</v>
+        <v>0.00021916971269670543</v>
       </c>
       <c r="Q3">
-        <v>0.00030059032528016185</v>
+        <v>0.00033213247295246382</v>
       </c>
       <c r="R3">
-        <v>0.00021660237617516798</v>
+        <v>0.00024525505148135845</v>
       </c>
       <c r="S3">
-        <v>0.0002079362161228125</v>
+        <v>0.00022247914151527284</v>
       </c>
       <c r="T3">
-        <v>0.00027631341562180079</v>
+        <v>0.00029151588484822421</v>
       </c>
       <c r="U3">
-        <v>0.00019166427248898388</v>
+        <v>0.00022378493367959489</v>
       </c>
       <c r="V3">
-        <v>0.00023579903342900725</v>
+        <v>0.00028890468513969735</v>
       </c>
       <c r="W3">
-        <v>0.00017986352000253186</v>
+        <v>0.00021055904214598411</v>
       </c>
       <c r="X3">
-        <v>0.00039292329618259461</v>
+        <v>0.00040755150323139224</v>
       </c>
       <c r="Y3">
-        <v>7.063291650684627e-005</v>
+        <v>8.9189338162662737e-005</v>
       </c>
       <c r="Z3">
-        <v>6.2381489539134298e-006</v>
+        <v>5.5465381527748832e-006</v>
       </c>
       <c r="AA3">
-        <v>1.7416438658738562e-005</v>
+        <v>-1.7573168729699581e-006</v>
       </c>
       <c r="AB3">
-        <v>-4.1134174872534601e-005</v>
+        <v>-4.672633855315857e-005</v>
       </c>
       <c r="AC3">
-        <v>-5.7744566046178877e-005</v>
+        <v>-5.1421144777178372e-005</v>
       </c>
       <c r="AD3">
-        <v>0.00023231043834136614</v>
+        <v>0.00025038700768558256</v>
       </c>
       <c r="AE3">
-        <v>2.6690207373225583e-005</v>
+        <v>3.1623440649669902e-005</v>
       </c>
       <c r="AF3">
-        <v>-0.016902746872015924</v>
+        <v>-0.017514934000154542</v>
       </c>
     </row>
     <row r="4">
@@ -733,97 +733,97 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>-0.0025240171622161458</v>
+        <v>-0.0026374910089944003</v>
       </c>
       <c r="C4">
-        <v>7.0552449275329866e-007</v>
+        <v>5.7940684815536636e-007</v>
       </c>
       <c r="D4">
-        <v>-2.1807274708357105e-005</v>
+        <v>-2.2742201372463721e-005</v>
       </c>
       <c r="E4">
-        <v>4.0360516416686558e-007</v>
+        <v>4.2203384982747703e-007</v>
       </c>
       <c r="F4">
-        <v>-1.2921120714149275e-005</v>
+        <v>-1.3182004074138322e-005</v>
       </c>
       <c r="G4">
-        <v>-8.0485452630270801e-006</v>
+        <v>-8.2040556567891323e-006</v>
       </c>
       <c r="H4">
-        <v>-1.0500480215670039e-005</v>
+        <v>-1.0886057665460501e-005</v>
       </c>
       <c r="I4">
-        <v>-1.0058556220471067e-005</v>
+        <v>-1.0312760726556718e-005</v>
       </c>
       <c r="J4">
-        <v>-8.3974461833759088e-006</v>
+        <v>-8.866953391535833e-006</v>
       </c>
       <c r="K4">
-        <v>-1.0302780444841522e-005</v>
+        <v>-1.0521364100166651e-005</v>
       </c>
       <c r="L4">
-        <v>-9.338226978776836e-006</v>
+        <v>-9.5408657135568446e-006</v>
       </c>
       <c r="M4">
-        <v>-9.2804015269248845e-006</v>
+        <v>-9.6651115286450413e-006</v>
       </c>
       <c r="N4">
-        <v>-1.2873544352199428e-005</v>
+        <v>-1.3196868707365523e-005</v>
       </c>
       <c r="O4">
-        <v>-4.5633697903885943e-006</v>
+        <v>-5.0103389523521421e-006</v>
       </c>
       <c r="P4">
-        <v>-4.4341052658777662e-006</v>
+        <v>-4.5763870343050955e-006</v>
       </c>
       <c r="Q4">
-        <v>-5.8352262043271684e-006</v>
+        <v>-6.4208637660308852e-006</v>
       </c>
       <c r="R4">
-        <v>-4.2505075881772647e-006</v>
+        <v>-4.7740958425850572e-006</v>
       </c>
       <c r="S4">
-        <v>-4.1798220484551469e-006</v>
+        <v>-4.4638876930843847e-006</v>
       </c>
       <c r="T4">
-        <v>-5.2013292076234029e-006</v>
+        <v>-5.5002422869261718e-006</v>
       </c>
       <c r="U4">
-        <v>-3.8649835366198458e-006</v>
+        <v>-4.4404589689473254e-006</v>
       </c>
       <c r="V4">
-        <v>-4.5594647668786777e-006</v>
+        <v>-5.5117995684629683e-006</v>
       </c>
       <c r="W4">
-        <v>-3.7516276753519595e-006</v>
+        <v>-4.3484124492790248e-006</v>
       </c>
       <c r="X4">
-        <v>-7.05062464731388e-006</v>
+        <v>-7.378021292163009e-006</v>
       </c>
       <c r="Y4">
-        <v>-1.6139807609959894e-006</v>
+        <v>-1.9618617589507151e-006</v>
       </c>
       <c r="Z4">
-        <v>-1.1663576159463862e-007</v>
+        <v>-1.0277630215341281e-007</v>
       </c>
       <c r="AA4">
-        <v>-3.5598869384956496e-007</v>
+        <v>-1.9788895121810917e-008</v>
       </c>
       <c r="AB4">
-        <v>6.001557713089116e-007</v>
+        <v>6.4379934628539128e-007</v>
       </c>
       <c r="AC4">
-        <v>8.9701446253503958e-007</v>
+        <v>7.8005903958221288e-007</v>
       </c>
       <c r="AD4">
-        <v>-5.4639387720562785e-006</v>
+        <v>-5.7861282063362827e-006</v>
       </c>
       <c r="AE4">
-        <v>-1.0366898333491296e-006</v>
+        <v>-1.0915277513781723e-006</v>
       </c>
       <c r="AF4">
-        <v>0.00030605520929484053</v>
+        <v>0.00031826043205515137</v>
       </c>
     </row>
     <row r="5">
@@ -831,97 +831,97 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>-0.068338977171936252</v>
+        <v>-0.046575993899235925</v>
       </c>
       <c r="C5">
-        <v>-0.00021197938057616363</v>
+        <v>-0.00020928808830303664</v>
       </c>
       <c r="D5">
-        <v>0.00073597551318355841</v>
+        <v>0.00074785210010035403</v>
       </c>
       <c r="E5">
-        <v>-1.2921120714149275e-005</v>
+        <v>-1.3182004074138322e-005</v>
       </c>
       <c r="F5">
-        <v>0.0068861210697293953</v>
+        <v>0.006783126919330645</v>
       </c>
       <c r="G5">
-        <v>0.0016703974733590676</v>
+        <v>0.0016552924588776412</v>
       </c>
       <c r="H5">
-        <v>0.0013927869406455506</v>
+        <v>0.0014002152644644402</v>
       </c>
       <c r="I5">
-        <v>-0.0033958625080570759</v>
+        <v>-0.0033287152441434107</v>
       </c>
       <c r="J5">
-        <v>-0.00050317726588124936</v>
+        <v>-0.00048101574809046761</v>
       </c>
       <c r="K5">
-        <v>-0.00025943564064329289</v>
+        <v>-0.00023016352705942087</v>
       </c>
       <c r="L5">
-        <v>-0.00061279203010486437</v>
+        <v>-0.00056111803503271608</v>
       </c>
       <c r="M5">
-        <v>-0.00044236983159325088</v>
+        <v>-0.00039710311581508012</v>
       </c>
       <c r="N5">
-        <v>-0.00043784190431948563</v>
+        <v>-0.00038923472375947165</v>
       </c>
       <c r="O5">
-        <v>0.00016037263962117264</v>
+        <v>0.00017552040504469676</v>
       </c>
       <c r="P5">
-        <v>5.812739636580069e-005</v>
+        <v>7.8055030679995922e-005</v>
       </c>
       <c r="Q5">
-        <v>7.4826797288005749e-005</v>
+        <v>0.00012257753311536231</v>
       </c>
       <c r="R5">
-        <v>0.00019724069310306133</v>
+        <v>0.00021272113071302116</v>
       </c>
       <c r="S5">
-        <v>3.0487714189990833e-005</v>
+        <v>1.068681583784605e-005</v>
       </c>
       <c r="T5">
-        <v>-5.7998533885439461e-005</v>
+        <v>-4.8702772164874219e-005</v>
       </c>
       <c r="U5">
-        <v>0.00031801106009928274</v>
+        <v>0.00034230433020416206</v>
       </c>
       <c r="V5">
-        <v>-5.1069468318189616e-005</v>
+        <v>-1.9939031848869313e-005</v>
       </c>
       <c r="W5">
-        <v>9.3417537433968575e-006</v>
+        <v>4.4493988832149459e-005</v>
       </c>
       <c r="X5">
-        <v>0.0004424192836913909</v>
+        <v>0.00048886398706520222</v>
       </c>
       <c r="Y5">
-        <v>-2.4534220518027117e-007</v>
+        <v>3.0788493923608086e-005</v>
       </c>
       <c r="Z5">
-        <v>5.4229481479521656e-005</v>
+        <v>5.1608625830742451e-005</v>
       </c>
       <c r="AA5">
-        <v>2.3277202756666512e-005</v>
+        <v>-1.1134448375686896e-005</v>
       </c>
       <c r="AB5">
-        <v>-4.2837285484760611e-005</v>
+        <v>-4.3743892798587506e-005</v>
       </c>
       <c r="AC5">
-        <v>-5.9713529081658126e-006</v>
+        <v>1.2690773982487573e-005</v>
       </c>
       <c r="AD5">
-        <v>0.00093280133627342884</v>
+        <v>0.00094297749891236304</v>
       </c>
       <c r="AE5">
-        <v>-0.00021567594819360959</v>
+        <v>-0.00016788434318726515</v>
       </c>
       <c r="AF5">
-        <v>-0.011634867584163894</v>
+        <v>-0.011777815928539704</v>
       </c>
     </row>
     <row r="6">
@@ -929,97 +929,97 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>-0.20029080612282846</v>
+        <v>-0.19764507198603429</v>
       </c>
       <c r="C6">
-        <v>-0.00014406465454916244</v>
+        <v>-0.00014213747318839987</v>
       </c>
       <c r="D6">
-        <v>0.00044698515438757174</v>
+        <v>0.00045482078467390798</v>
       </c>
       <c r="E6">
-        <v>-8.0485452630270801e-006</v>
+        <v>-8.2040556567891323e-006</v>
       </c>
       <c r="F6">
-        <v>0.0016703974733590676</v>
+        <v>0.0016552924588776412</v>
       </c>
       <c r="G6">
-        <v>0.0016900453741976193</v>
+        <v>0.0016676720873519228</v>
       </c>
       <c r="H6">
-        <v>0.0013334020047796396</v>
+        <v>0.001338407489425349</v>
       </c>
       <c r="I6">
-        <v>-0.00020532015773686908</v>
+        <v>-0.00020428242260559599</v>
       </c>
       <c r="J6">
-        <v>-6.2262512534164626e-005</v>
+        <v>-8.3415399622898778e-005</v>
       </c>
       <c r="K6">
-        <v>6.3509100242202347e-005</v>
+        <v>5.2196315047691073e-005</v>
       </c>
       <c r="L6">
-        <v>-2.8746441952381008e-006</v>
+        <v>1.6017990901286486e-006</v>
       </c>
       <c r="M6">
-        <v>0.00022036436742241277</v>
+        <v>0.00021416430979306661</v>
       </c>
       <c r="N6">
-        <v>0.00030783586733345355</v>
+        <v>0.00031115394524307391</v>
       </c>
       <c r="O6">
-        <v>0.00041458236174911052</v>
+        <v>0.000425331907130092</v>
       </c>
       <c r="P6">
-        <v>0.00037845205857620556</v>
+        <v>0.00038750367103964007</v>
       </c>
       <c r="Q6">
-        <v>0.00021444698103237987</v>
+        <v>0.00023291613436434257</v>
       </c>
       <c r="R6">
-        <v>0.00019391979829262506</v>
+        <v>0.00020437215978698611</v>
       </c>
       <c r="S6">
-        <v>0.00025811460608230266</v>
+        <v>0.00023964805423711466</v>
       </c>
       <c r="T6">
-        <v>0.00017318871733665943</v>
+        <v>0.00018255517519527977</v>
       </c>
       <c r="U6">
-        <v>0.00043702534909603069</v>
+        <v>0.00043970249710389661</v>
       </c>
       <c r="V6">
-        <v>0.00011673572119270763</v>
+        <v>0.00011515613050978781</v>
       </c>
       <c r="W6">
-        <v>0.00021077573410292836</v>
+        <v>0.00023546423936156432</v>
       </c>
       <c r="X6">
-        <v>0.00047431797428717907</v>
+        <v>0.00046663588295321756</v>
       </c>
       <c r="Y6">
-        <v>0.00026229625072693571</v>
+        <v>0.00027453127911696842</v>
       </c>
       <c r="Z6">
-        <v>3.2268393460251261e-005</v>
+        <v>2.9394776555972057e-005</v>
       </c>
       <c r="AA6">
-        <v>-0.00015900841811044463</v>
+        <v>-0.00014976418133005764</v>
       </c>
       <c r="AB6">
-        <v>-7.3833880595032368e-005</v>
+        <v>-5.0201176582674524e-005</v>
       </c>
       <c r="AC6">
-        <v>0.00031586741325373684</v>
+        <v>0.00032553682570858221</v>
       </c>
       <c r="AD6">
-        <v>0.0010093788417061046</v>
+        <v>0.0009958487500214214</v>
       </c>
       <c r="AE6">
-        <v>-0.00011602191616720341</v>
+        <v>-9.529260626359626e-005</v>
       </c>
       <c r="AF6">
-        <v>-0.0079889883797299027</v>
+        <v>-0.0080302498767641749</v>
       </c>
     </row>
     <row r="7">
@@ -1027,97 +1027,97 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-0.40892261351243714</v>
+        <v>-0.39715703200294961</v>
       </c>
       <c r="C7">
-        <v>-0.00030140793155994844</v>
+        <v>-0.00028077360736408308</v>
       </c>
       <c r="D7">
-        <v>0.00056499682685125111</v>
+        <v>0.00058322308148082568</v>
       </c>
       <c r="E7">
-        <v>-1.0500480215670039e-005</v>
+        <v>-1.0886057665460501e-005</v>
       </c>
       <c r="F7">
-        <v>0.0013927869406455506</v>
+        <v>0.0014002152644644402</v>
       </c>
       <c r="G7">
-        <v>0.0013334020047796396</v>
+        <v>0.001338407489425349</v>
       </c>
       <c r="H7">
-        <v>0.0072581226604306881</v>
+        <v>0.0069021390870677079</v>
       </c>
       <c r="I7">
-        <v>0.0003113655990207246</v>
+        <v>0.00026996963530662946</v>
       </c>
       <c r="J7">
-        <v>-0.00030009325923867358</v>
+        <v>-0.0003458631009336672</v>
       </c>
       <c r="K7">
-        <v>0.0007527270748285738</v>
+        <v>0.00068765806952772717</v>
       </c>
       <c r="L7">
-        <v>0.00058564043010910524</v>
+        <v>0.00053760314821295753</v>
       </c>
       <c r="M7">
-        <v>0.00086232719808259728</v>
+        <v>0.00080254992244528818</v>
       </c>
       <c r="N7">
-        <v>0.00093647388049622937</v>
+        <v>0.00091594319091912861</v>
       </c>
       <c r="O7">
-        <v>0.00054815717938424906</v>
+        <v>0.00051117033293162652</v>
       </c>
       <c r="P7">
-        <v>0.0003176515552736675</v>
+        <v>0.00029781773303729398</v>
       </c>
       <c r="Q7">
-        <v>0.00032281677300110184</v>
+        <v>0.00032096454713878157</v>
       </c>
       <c r="R7">
-        <v>0.00027077130084104787</v>
+        <v>0.00024491604112460407</v>
       </c>
       <c r="S7">
-        <v>-5.277371719381637e-005</v>
+        <v>-8.2862081123117074e-005</v>
       </c>
       <c r="T7">
-        <v>-0.00018899969872881436</v>
+        <v>-0.00015866347838978619</v>
       </c>
       <c r="U7">
-        <v>0.00018180829151978953</v>
+        <v>0.00020045470572709187</v>
       </c>
       <c r="V7">
-        <v>9.460330328559945e-005</v>
+        <v>8.460444925412696e-005</v>
       </c>
       <c r="W7">
-        <v>-0.00029061778133209826</v>
+        <v>-0.00027289333462918424</v>
       </c>
       <c r="X7">
-        <v>0.00025288903893850879</v>
+        <v>0.00025721441367772046</v>
       </c>
       <c r="Y7">
-        <v>-0.00017878376142649441</v>
+        <v>-0.00015137127251240085</v>
       </c>
       <c r="Z7">
-        <v>6.6193986219103542e-006</v>
+        <v>2.8983402962123091e-006</v>
       </c>
       <c r="AA7">
-        <v>7.0332452522272465e-005</v>
+        <v>8.1238770249010377e-005</v>
       </c>
       <c r="AB7">
-        <v>-4.0582446417701252e-005</v>
+        <v>-2.0613297126215776e-005</v>
       </c>
       <c r="AC7">
-        <v>0.00047216564744282622</v>
+        <v>0.0004793425591367354</v>
       </c>
       <c r="AD7">
-        <v>0.00072591868540034486</v>
+        <v>0.00070980837334838924</v>
       </c>
       <c r="AE7">
-        <v>-0.00011953630469916949</v>
+        <v>-5.4739881428440265e-005</v>
       </c>
       <c r="AF7">
-        <v>-0.0092651409975657139</v>
+        <v>-0.0093680085557710947</v>
       </c>
     </row>
     <row r="8">
@@ -1125,97 +1125,97 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>-0.28150030739086995</v>
+        <v>-0.28442451085933707</v>
       </c>
       <c r="C8">
-        <v>0.00010992743708696897</v>
+        <v>0.00011693215038753348</v>
       </c>
       <c r="D8">
-        <v>0.00061373869255915408</v>
+        <v>0.00062552257235919334</v>
       </c>
       <c r="E8">
-        <v>-1.0058556220471067e-005</v>
+        <v>-1.0312760726556718e-005</v>
       </c>
       <c r="F8">
-        <v>-0.0033958625080570759</v>
+        <v>-0.0033287152441434107</v>
       </c>
       <c r="G8">
-        <v>-0.00020532015773686908</v>
+        <v>-0.00020428242260559599</v>
       </c>
       <c r="H8">
-        <v>0.0003113655990207246</v>
+        <v>0.00026996963530662946</v>
       </c>
       <c r="I8">
-        <v>0.0061503914532539741</v>
+        <v>0.0060089826880800612</v>
       </c>
       <c r="J8">
-        <v>0.0028696470455798449</v>
+        <v>0.0028254367467958523</v>
       </c>
       <c r="K8">
-        <v>0.0026778135298235937</v>
+        <v>0.0026281572233764787</v>
       </c>
       <c r="L8">
-        <v>0.003478437350683154</v>
+        <v>0.0033715649643565526</v>
       </c>
       <c r="M8">
-        <v>0.0031800770395106833</v>
+        <v>0.0030826209989082945</v>
       </c>
       <c r="N8">
-        <v>0.0026008734829236131</v>
+        <v>0.002513301816451154</v>
       </c>
       <c r="O8">
-        <v>-0.00016896273232146924</v>
+        <v>-0.00018202256515820669</v>
       </c>
       <c r="P8">
-        <v>-0.00011621209591009939</v>
+        <v>-0.00012842711053999249</v>
       </c>
       <c r="Q8">
-        <v>0.0001015586772983543</v>
+        <v>8.4685382186537551e-005</v>
       </c>
       <c r="R8">
-        <v>-7.8784182296940384e-005</v>
+        <v>-8.1775848537707352e-005</v>
       </c>
       <c r="S8">
-        <v>-0.00017870944201391027</v>
+        <v>-0.00016426467398710821</v>
       </c>
       <c r="T8">
-        <v>0.00013078946834898001</v>
+        <v>0.00013280946826447722</v>
       </c>
       <c r="U8">
-        <v>-0.00020251013834823297</v>
+        <v>-0.00019874842424609475</v>
       </c>
       <c r="V8">
-        <v>3.1072259535607567e-005</v>
+        <v>0.00010485499664486639</v>
       </c>
       <c r="W8">
-        <v>-1.0386168376098253e-005</v>
+        <v>-1.9790987203760577e-005</v>
       </c>
       <c r="X8">
-        <v>-0.00043857718608658841</v>
+        <v>-0.00043595354744736564</v>
       </c>
       <c r="Y8">
-        <v>-3.0225521183643161e-005</v>
+        <v>-4.569076716493068e-005</v>
       </c>
       <c r="Z8">
-        <v>-4.1365468926742727e-005</v>
+        <v>-3.7555828676394745e-005</v>
       </c>
       <c r="AA8">
-        <v>-0.00011250905909482908</v>
+        <v>-8.6283811761349058e-005</v>
       </c>
       <c r="AB8">
-        <v>4.9325869880878287e-005</v>
+        <v>2.1894137232975801e-005</v>
       </c>
       <c r="AC8">
-        <v>0.00026098310407256589</v>
+        <v>0.00024296540258966423</v>
       </c>
       <c r="AD8">
-        <v>-0.0006662390109181543</v>
+        <v>-0.0006613609584761428</v>
       </c>
       <c r="AE8">
-        <v>-3.7175424572115931e-005</v>
+        <v>-5.7073530645228862e-005</v>
       </c>
       <c r="AF8">
-        <v>-0.011543899938597269</v>
+        <v>-0.011643344785943179</v>
       </c>
     </row>
     <row r="9">
@@ -1223,97 +1223,97 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-0.32308011396191771</v>
+        <v>-0.31256654149451091</v>
       </c>
       <c r="C9">
-        <v>-6.3586271895521706e-005</v>
+        <v>-6.8444517816496439e-005</v>
       </c>
       <c r="D9">
-        <v>0.00049644080088420283</v>
+        <v>0.00052269196264448066</v>
       </c>
       <c r="E9">
-        <v>-8.3974461833759088e-006</v>
+        <v>-8.866953391535833e-006</v>
       </c>
       <c r="F9">
-        <v>-0.00050317726588124936</v>
+        <v>-0.00048101574809046761</v>
       </c>
       <c r="G9">
-        <v>-6.2262512534164626e-005</v>
+        <v>-8.3415399622898778e-005</v>
       </c>
       <c r="H9">
-        <v>-0.00030009325923867358</v>
+        <v>-0.0003458631009336672</v>
       </c>
       <c r="I9">
-        <v>0.0028696470455798449</v>
+        <v>0.0028254367467958523</v>
       </c>
       <c r="J9">
-        <v>0.0039013575491415398</v>
+        <v>0.0038697969496396169</v>
       </c>
       <c r="K9">
-        <v>0.00229821996811459</v>
+        <v>0.0023270390801340725</v>
       </c>
       <c r="L9">
-        <v>0.0030078565631428767</v>
+        <v>0.0029807291595275072</v>
       </c>
       <c r="M9">
-        <v>0.0028099351714687866</v>
+        <v>0.0027801905113930738</v>
       </c>
       <c r="N9">
-        <v>0.0021658246235069425</v>
+        <v>0.0021365057966907458</v>
       </c>
       <c r="O9">
-        <v>-0.00045447257724709413</v>
+        <v>-0.00042287485381961305</v>
       </c>
       <c r="P9">
-        <v>-0.00019945192709842517</v>
+        <v>-0.00018912045783531228</v>
       </c>
       <c r="Q9">
-        <v>7.8046457099332253e-005</v>
+        <v>7.2347178632508366e-005</v>
       </c>
       <c r="R9">
-        <v>-0.00025891891098770456</v>
+        <v>-0.00022824039109469531</v>
       </c>
       <c r="S9">
-        <v>-0.00011097770649574077</v>
+        <v>-0.00010352144696709341</v>
       </c>
       <c r="T9">
-        <v>9.2760294381045256e-005</v>
+        <v>9.410148428282551e-005</v>
       </c>
       <c r="U9">
-        <v>-2.2676695775995966e-005</v>
+        <v>-2.9382869025809319e-005</v>
       </c>
       <c r="V9">
-        <v>-0.00010739347382454037</v>
+        <v>8.9401227001010891e-006</v>
       </c>
       <c r="W9">
-        <v>-2.2264799040716326e-005</v>
+        <v>-2.159535163679554e-005</v>
       </c>
       <c r="X9">
-        <v>-0.00032945400874874464</v>
+        <v>-0.00030335970941101518</v>
       </c>
       <c r="Y9">
-        <v>-5.7069399919435979e-005</v>
+        <v>-4.8778623024560951e-005</v>
       </c>
       <c r="Z9">
-        <v>-2.7516889140124373e-005</v>
+        <v>-2.2044062251088108e-005</v>
       </c>
       <c r="AA9">
-        <v>-0.00012532430826556602</v>
+        <v>-0.00013068494898034382</v>
       </c>
       <c r="AB9">
-        <v>6.6643847136751066e-005</v>
+        <v>2.8965319935750247e-005</v>
       </c>
       <c r="AC9">
-        <v>0.00013984009935072515</v>
+        <v>0.00011857043577067228</v>
       </c>
       <c r="AD9">
-        <v>-0.00041315936917586584</v>
+        <v>-0.00039227205058577595</v>
       </c>
       <c r="AE9">
-        <v>-2.4776596705223001e-005</v>
+        <v>-4.0313732663310058e-005</v>
       </c>
       <c r="AF9">
-        <v>-0.0094594150932819053</v>
+        <v>-0.0098749837216438457</v>
       </c>
     </row>
     <row r="10">
@@ -1321,97 +1321,97 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-0.13588066706684404</v>
+        <v>-0.13748350081147806</v>
       </c>
       <c r="C10">
-        <v>-2.9641244509623939e-005</v>
+        <v>-3.6853875254175703e-005</v>
       </c>
       <c r="D10">
-        <v>0.00062217875906899498</v>
+        <v>0.00063209572422124585</v>
       </c>
       <c r="E10">
-        <v>-1.0302780444841522e-005</v>
+        <v>-1.0521364100166651e-005</v>
       </c>
       <c r="F10">
-        <v>-0.00025943564064329289</v>
+        <v>-0.00023016352705942087</v>
       </c>
       <c r="G10">
-        <v>6.3509100242202347e-005</v>
+        <v>5.2196315047691073e-005</v>
       </c>
       <c r="H10">
-        <v>0.0007527270748285738</v>
+        <v>0.00068765806952772717</v>
       </c>
       <c r="I10">
-        <v>0.0026778135298235937</v>
+        <v>0.0026281572233764787</v>
       </c>
       <c r="J10">
-        <v>0.00229821996811459</v>
+        <v>0.0023270390801340725</v>
       </c>
       <c r="K10">
-        <v>0.0042681375593123499</v>
+        <v>0.0042023904464803027</v>
       </c>
       <c r="L10">
-        <v>0.0031308632923174326</v>
+        <v>0.0030925612400729847</v>
       </c>
       <c r="M10">
-        <v>0.002929147520990532</v>
+        <v>0.0028963976260684581</v>
       </c>
       <c r="N10">
-        <v>0.0025164059741901862</v>
+        <v>0.0024845908830676681</v>
       </c>
       <c r="O10">
-        <v>4.8948648079161347e-005</v>
+        <v>6.0755013996326244e-005</v>
       </c>
       <c r="P10">
-        <v>-0.00039332451050989653</v>
+        <v>-0.0003428545400898232</v>
       </c>
       <c r="Q10">
-        <v>3.9284211488679432e-005</v>
+        <v>3.9354669028877128e-005</v>
       </c>
       <c r="R10">
-        <v>-0.00030452664278785962</v>
+        <v>-0.00026979754605460139</v>
       </c>
       <c r="S10">
-        <v>-0.00028883730445634025</v>
+        <v>-0.00028655286503329156</v>
       </c>
       <c r="T10">
-        <v>-8.2853231408423972e-005</v>
+        <v>-5.2620313204844677e-005</v>
       </c>
       <c r="U10">
-        <v>-0.00011272713776758572</v>
+        <v>-0.00010007578409842901</v>
       </c>
       <c r="V10">
-        <v>-1.6199263216596684e-005</v>
+        <v>0.00010283148016374758</v>
       </c>
       <c r="W10">
-        <v>-0.00029733774912710166</v>
+        <v>-0.00027214372833735362</v>
       </c>
       <c r="X10">
-        <v>0.00010930006450980787</v>
+        <v>0.00010489516307815301</v>
       </c>
       <c r="Y10">
-        <v>-4.8141479433951549e-005</v>
+        <v>-3.0747806066477694e-005</v>
       </c>
       <c r="Z10">
-        <v>-6.9384629440293099e-006</v>
+        <v>-2.3510275671065209e-006</v>
       </c>
       <c r="AA10">
-        <v>-0.00014738160509518758</v>
+        <v>-0.00015745810876441126</v>
       </c>
       <c r="AB10">
-        <v>2.7648801358822958e-006</v>
+        <v>-2.7678162264313804e-005</v>
       </c>
       <c r="AC10">
-        <v>0.0002051387955296774</v>
+        <v>0.00019642548064529577</v>
       </c>
       <c r="AD10">
-        <v>-0.00014962454686858178</v>
+        <v>-0.00013283565489415495</v>
       </c>
       <c r="AE10">
-        <v>-3.0191651593918086e-005</v>
+        <v>-3.678219805361481e-005</v>
       </c>
       <c r="AF10">
-        <v>-0.011901656189561797</v>
+        <v>-0.012062052359739724</v>
       </c>
     </row>
     <row r="11">
@@ -1419,97 +1419,97 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>-0.31087728496190936</v>
+        <v>-0.30234471591739631</v>
       </c>
       <c r="C11">
-        <v>-1.0368023249293773e-005</v>
+        <v>-2.2440980154536251e-005</v>
       </c>
       <c r="D11">
-        <v>0.00055792788299802512</v>
+        <v>0.00056749030562737966</v>
       </c>
       <c r="E11">
-        <v>-9.338226978776836e-006</v>
+        <v>-9.5408657135568446e-006</v>
       </c>
       <c r="F11">
-        <v>-0.00061279203010486437</v>
+        <v>-0.00056111803503271608</v>
       </c>
       <c r="G11">
-        <v>-2.8746441952381008e-006</v>
+        <v>1.6017990901286486e-006</v>
       </c>
       <c r="H11">
-        <v>0.00058564043010910524</v>
+        <v>0.00053760314821295753</v>
       </c>
       <c r="I11">
-        <v>0.003478437350683154</v>
+        <v>0.0033715649643565526</v>
       </c>
       <c r="J11">
-        <v>0.0030078565631428767</v>
+        <v>0.0029807291595275072</v>
       </c>
       <c r="K11">
-        <v>0.0031308632923174326</v>
+        <v>0.0030925612400729847</v>
       </c>
       <c r="L11">
-        <v>0.0047296076479753394</v>
+        <v>0.0046114744635975327</v>
       </c>
       <c r="M11">
-        <v>0.0035930876897090087</v>
+        <v>0.0035045593942646175</v>
       </c>
       <c r="N11">
-        <v>0.0029508381497041964</v>
+        <v>0.0028763621068475958</v>
       </c>
       <c r="O11">
-        <v>0.00017646295254514438</v>
+        <v>0.00014006089278186667</v>
       </c>
       <c r="P11">
-        <v>-0.00028542934191575159</v>
+        <v>-0.00024104238801312327</v>
       </c>
       <c r="Q11">
-        <v>-1.4715983564685424e-005</v>
+        <v>-3.7503622150512569e-005</v>
       </c>
       <c r="R11">
-        <v>-0.00027995558856231442</v>
+        <v>-0.00026172850415994402</v>
       </c>
       <c r="S11">
-        <v>-0.00017497526215940027</v>
+        <v>-0.00019962571270795313</v>
       </c>
       <c r="T11">
-        <v>-0.00012738039146002414</v>
+        <v>-0.00012065154193495307</v>
       </c>
       <c r="U11">
-        <v>-0.00019477596782150491</v>
+        <v>-0.00018710133741960686</v>
       </c>
       <c r="V11">
-        <v>-0.00010281932410645725</v>
+        <v>-3.8076447667331e-005</v>
       </c>
       <c r="W11">
-        <v>-0.00014030637654814551</v>
+        <v>-0.00014170826613530666</v>
       </c>
       <c r="X11">
-        <v>-0.00043012428892554976</v>
+        <v>-0.00042082317678292485</v>
       </c>
       <c r="Y11">
-        <v>-5.7485889338725407e-005</v>
+        <v>-7.0070697932111611e-005</v>
       </c>
       <c r="Z11">
-        <v>-1.34778923736856e-005</v>
+        <v>-1.053029378086435e-005</v>
       </c>
       <c r="AA11">
-        <v>-0.00018271531471755498</v>
+        <v>-0.0001626795232896356</v>
       </c>
       <c r="AB11">
-        <v>0.00011944581315777194</v>
+        <v>0.00013111708089886599</v>
       </c>
       <c r="AC11">
-        <v>0.00030886337408375479</v>
+        <v>0.00028942878634061371</v>
       </c>
       <c r="AD11">
-        <v>-0.00025962958563299516</v>
+        <v>-0.00030057455987180307</v>
       </c>
       <c r="AE11">
-        <v>7.8277593571055232e-005</v>
+        <v>6.756641963733196e-005</v>
       </c>
       <c r="AF11">
-        <v>-0.011446684140591565</v>
+        <v>-0.01152302452652448</v>
       </c>
     </row>
     <row r="12">
@@ -1517,97 +1517,97 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>-0.16136587827359497</v>
+        <v>-0.15996082097943842</v>
       </c>
       <c r="C12">
-        <v>6.1358318463479801e-006</v>
+        <v>-8.9092834616001046e-006</v>
       </c>
       <c r="D12">
-        <v>0.00052508275896529725</v>
+        <v>0.00054614448249212767</v>
       </c>
       <c r="E12">
-        <v>-9.2804015269248845e-006</v>
+        <v>-9.6651115286450413e-006</v>
       </c>
       <c r="F12">
-        <v>-0.00044236983159325088</v>
+        <v>-0.00039710311581508012</v>
       </c>
       <c r="G12">
-        <v>0.00022036436742241277</v>
+        <v>0.00021416430979306661</v>
       </c>
       <c r="H12">
-        <v>0.00086232719808259728</v>
+        <v>0.00080254992244528818</v>
       </c>
       <c r="I12">
-        <v>0.0031800770395106833</v>
+        <v>0.0030826209989082945</v>
       </c>
       <c r="J12">
-        <v>0.0028099351714687866</v>
+        <v>0.0027801905113930738</v>
       </c>
       <c r="K12">
-        <v>0.002929147520990532</v>
+        <v>0.0028963976260684581</v>
       </c>
       <c r="L12">
-        <v>0.0035930876897090087</v>
+        <v>0.0035045593942646175</v>
       </c>
       <c r="M12">
-        <v>0.0045208786401440965</v>
+        <v>0.0044063715369492109</v>
       </c>
       <c r="N12">
-        <v>0.0028516572842618654</v>
+        <v>0.0027731843332169225</v>
       </c>
       <c r="O12">
-        <v>-8.687659559375731e-005</v>
+        <v>-6.2464533415696518e-005</v>
       </c>
       <c r="P12">
-        <v>0.00015437615436957519</v>
+        <v>0.00016387214663320191</v>
       </c>
       <c r="Q12">
-        <v>0.00033622633650817974</v>
+        <v>0.00032231913275913371</v>
       </c>
       <c r="R12">
-        <v>-0.0001212867631756516</v>
+        <v>-9.9778175767282963e-005</v>
       </c>
       <c r="S12">
-        <v>-0.00011168416915693772</v>
+        <v>-0.00010914618536152806</v>
       </c>
       <c r="T12">
-        <v>-8.183642104436274e-005</v>
+        <v>-5.0768722785341858e-005</v>
       </c>
       <c r="U12">
-        <v>0.00019276706255083229</v>
+        <v>0.00018623961052561676</v>
       </c>
       <c r="V12">
-        <v>4.630706637586161e-007</v>
+        <v>0.00010554757078274897</v>
       </c>
       <c r="W12">
-        <v>0.00020039211946581764</v>
+        <v>0.00022004732524477416</v>
       </c>
       <c r="X12">
-        <v>-0.00020713612021222409</v>
+        <v>-0.00017493195207135017</v>
       </c>
       <c r="Y12">
-        <v>0.0001459941279289478</v>
+        <v>0.00015378535548162507</v>
       </c>
       <c r="Z12">
-        <v>2.4024028695788244e-006</v>
+        <v>6.5363914788635607e-006</v>
       </c>
       <c r="AA12">
-        <v>-0.00021619057127154258</v>
+        <v>-0.00020573075219414654</v>
       </c>
       <c r="AB12">
-        <v>0.00011150563132992673</v>
+        <v>7.5137056719524662e-005</v>
       </c>
       <c r="AC12">
-        <v>0.00036882729498072513</v>
+        <v>0.00035175900263562272</v>
       </c>
       <c r="AD12">
-        <v>0.00093441398487588076</v>
+        <v>0.00093745277932571515</v>
       </c>
       <c r="AE12">
-        <v>0.0002959661078906794</v>
+        <v>0.00028017165294491901</v>
       </c>
       <c r="AF12">
-        <v>-0.0111729166654637</v>
+        <v>-0.011436455466038706</v>
       </c>
     </row>
     <row r="13">
@@ -1615,97 +1615,97 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>-0.068421235255630333</v>
+        <v>-0.072382470861623985</v>
       </c>
       <c r="C13">
-        <v>-6.5427681280571192e-005</v>
+        <v>-7.0962650636526443e-005</v>
       </c>
       <c r="D13">
-        <v>0.00072309083467292238</v>
+        <v>0.00074007853589422171</v>
       </c>
       <c r="E13">
-        <v>-1.2873544352199428e-005</v>
+        <v>-1.3196868707365523e-005</v>
       </c>
       <c r="F13">
-        <v>-0.00043784190431948563</v>
+        <v>-0.00038923472375947165</v>
       </c>
       <c r="G13">
-        <v>0.00030783586733345355</v>
+        <v>0.00031115394524307391</v>
       </c>
       <c r="H13">
-        <v>0.00093647388049622937</v>
+        <v>0.00091594319091912861</v>
       </c>
       <c r="I13">
-        <v>0.0026008734829236131</v>
+        <v>0.002513301816451154</v>
       </c>
       <c r="J13">
-        <v>0.0021658246235069425</v>
+        <v>0.0021365057966907458</v>
       </c>
       <c r="K13">
-        <v>0.0025164059741901862</v>
+        <v>0.0024845908830676681</v>
       </c>
       <c r="L13">
-        <v>0.0029508381497041964</v>
+        <v>0.0028763621068475958</v>
       </c>
       <c r="M13">
-        <v>0.0028516572842618654</v>
+        <v>0.0027731843332169225</v>
       </c>
       <c r="N13">
-        <v>0.0050141988240940188</v>
+        <v>0.0049144499226467632</v>
       </c>
       <c r="O13">
-        <v>0.00012172473532677118</v>
+        <v>0.00011595328373372252</v>
       </c>
       <c r="P13">
-        <v>0.00013209034582392729</v>
+        <v>0.00013439879369978947</v>
       </c>
       <c r="Q13">
-        <v>0.00032485661051898692</v>
+        <v>0.00029894130618722211</v>
       </c>
       <c r="R13">
-        <v>-0.00010201778916059867</v>
+        <v>-9.1208594492976126e-005</v>
       </c>
       <c r="S13">
-        <v>3.4634591117102282e-006</v>
+        <v>-2.7246929796371708e-008</v>
       </c>
       <c r="T13">
-        <v>0.00023011720666271608</v>
+        <v>0.00023897692962961202</v>
       </c>
       <c r="U13">
-        <v>5.244897218382831e-005</v>
+        <v>4.0710872103126919e-005</v>
       </c>
       <c r="V13">
-        <v>4.9712087249859072e-005</v>
+        <v>0.00012970008258914338</v>
       </c>
       <c r="W13">
-        <v>0.00017063826866511736</v>
+        <v>0.0001632664983259079</v>
       </c>
       <c r="X13">
-        <v>-0.00019682366098021039</v>
+        <v>-0.00019104519575067233</v>
       </c>
       <c r="Y13">
-        <v>0.00020044876780360259</v>
+        <v>0.00017950162568103768</v>
       </c>
       <c r="Z13">
-        <v>-2.8348228349493266e-005</v>
+        <v>-2.3723803880397378e-005</v>
       </c>
       <c r="AA13">
-        <v>-0.00019430985241639744</v>
+        <v>-0.00021449840702193014</v>
       </c>
       <c r="AB13">
-        <v>0.00017872220122624669</v>
+        <v>0.00015369927807691109</v>
       </c>
       <c r="AC13">
-        <v>8.0825846154021497e-005</v>
+        <v>7.6739270380916588e-005</v>
       </c>
       <c r="AD13">
-        <v>-6.7322789170863942e-005</v>
+        <v>-0.00013411624186865801</v>
       </c>
       <c r="AE13">
-        <v>9.7717856914546685e-005</v>
+        <v>9.9494135433479962e-005</v>
       </c>
       <c r="AF13">
-        <v>-0.012635908038859202</v>
+        <v>-0.012853668771424229</v>
       </c>
     </row>
     <row r="14">
@@ -1713,97 +1713,97 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>-0.077041097515842108</v>
+        <v>-0.06584520843030145</v>
       </c>
       <c r="C14">
-        <v>-0.0001540994945668651</v>
+        <v>-0.00015518119750959294</v>
       </c>
       <c r="D14">
-        <v>0.00024806444867658817</v>
+        <v>0.00027035978605119285</v>
       </c>
       <c r="E14">
-        <v>-4.5633697903885943e-006</v>
+        <v>-5.0103389523521421e-006</v>
       </c>
       <c r="F14">
-        <v>0.00016037263962117264</v>
+        <v>0.00017552040504469676</v>
       </c>
       <c r="G14">
-        <v>0.00041458236174911052</v>
+        <v>0.000425331907130092</v>
       </c>
       <c r="H14">
-        <v>0.00054815717938424906</v>
+        <v>0.00051117033293162652</v>
       </c>
       <c r="I14">
-        <v>-0.00016896273232146924</v>
+        <v>-0.00018202256515820669</v>
       </c>
       <c r="J14">
-        <v>-0.00045447257724709413</v>
+        <v>-0.00042287485381961305</v>
       </c>
       <c r="K14">
-        <v>4.8948648079161347e-005</v>
+        <v>6.0755013996326244e-005</v>
       </c>
       <c r="L14">
-        <v>0.00017646295254514438</v>
+        <v>0.00014006089278186667</v>
       </c>
       <c r="M14">
-        <v>-8.687659559375731e-005</v>
+        <v>-6.2464533415696518e-005</v>
       </c>
       <c r="N14">
-        <v>0.00012172473532677118</v>
+        <v>0.00011595328373372252</v>
       </c>
       <c r="O14">
-        <v>0.010358038774061102</v>
+        <v>0.0099149368375718114</v>
       </c>
       <c r="P14">
-        <v>0.0025921236134118864</v>
+        <v>0.0025672734967308649</v>
       </c>
       <c r="Q14">
-        <v>0.0026512963125486693</v>
+        <v>0.0026256451612013685</v>
       </c>
       <c r="R14">
-        <v>0.0026527326154781529</v>
+        <v>0.002624626502797591</v>
       </c>
       <c r="S14">
-        <v>0.0024745579431253778</v>
+        <v>0.0024624398276962317</v>
       </c>
       <c r="T14">
-        <v>0.0026114294380400502</v>
+        <v>0.0025855034717256606</v>
       </c>
       <c r="U14">
-        <v>0.0030277306313199106</v>
+        <v>0.0029859753387207933</v>
       </c>
       <c r="V14">
-        <v>0.0027502628493991052</v>
+        <v>0.0027176783579206539</v>
       </c>
       <c r="W14">
-        <v>0.0027541630446469298</v>
+        <v>0.0027274676973273854</v>
       </c>
       <c r="X14">
-        <v>0.0027103462515041367</v>
+        <v>0.0026847055323007433</v>
       </c>
       <c r="Y14">
-        <v>0.0027503890877909063</v>
+        <v>0.002715518534505136</v>
       </c>
       <c r="Z14">
-        <v>5.4844656493688369e-005</v>
+        <v>5.1592949014426793e-005</v>
       </c>
       <c r="AA14">
-        <v>-0.00038748566674939834</v>
+        <v>-0.00035310705837768194</v>
       </c>
       <c r="AB14">
-        <v>-0.00036873138116462343</v>
+        <v>-0.00034395539638527872</v>
       </c>
       <c r="AC14">
-        <v>0.00091495896124979374</v>
+        <v>0.00088979808235138929</v>
       </c>
       <c r="AD14">
-        <v>0.0041337960087751528</v>
+        <v>0.0040565538540559797</v>
       </c>
       <c r="AE14">
-        <v>0.00069584599408913507</v>
+        <v>0.00068659941555398931</v>
       </c>
       <c r="AF14">
-        <v>-0.007059224968605015</v>
+        <v>-0.0072514304522253853</v>
       </c>
     </row>
     <row r="15">
@@ -1811,97 +1811,97 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>0.14915386667280536</v>
+        <v>0.17246642101542556</v>
       </c>
       <c r="C15">
-        <v>0.0001901710139219859</v>
+        <v>0.00016438002439312681</v>
       </c>
       <c r="D15">
-        <v>0.0002131504825218962</v>
+        <v>0.00021916971269670543</v>
       </c>
       <c r="E15">
-        <v>-4.4341052658777662e-006</v>
+        <v>-4.5763870343050955e-006</v>
       </c>
       <c r="F15">
-        <v>5.812739636580069e-005</v>
+        <v>7.8055030679995922e-005</v>
       </c>
       <c r="G15">
-        <v>0.00037845205857620556</v>
+        <v>0.00038750367103964007</v>
       </c>
       <c r="H15">
-        <v>0.0003176515552736675</v>
+        <v>0.00029781773303729398</v>
       </c>
       <c r="I15">
-        <v>-0.00011621209591009939</v>
+        <v>-0.00012842711053999249</v>
       </c>
       <c r="J15">
-        <v>-0.00019945192709842517</v>
+        <v>-0.00018912045783531228</v>
       </c>
       <c r="K15">
-        <v>-0.00039332451050989653</v>
+        <v>-0.0003428545400898232</v>
       </c>
       <c r="L15">
-        <v>-0.00028542934191575159</v>
+        <v>-0.00024104238801312327</v>
       </c>
       <c r="M15">
-        <v>0.00015437615436957519</v>
+        <v>0.00016387214663320191</v>
       </c>
       <c r="N15">
-        <v>0.00013209034582392729</v>
+        <v>0.00013439879369978947</v>
       </c>
       <c r="O15">
-        <v>0.0025921236134118864</v>
+        <v>0.0025672734967308649</v>
       </c>
       <c r="P15">
-        <v>0.0050599052678630381</v>
+        <v>0.0049501267289876133</v>
       </c>
       <c r="Q15">
-        <v>0.0026023254588194746</v>
+        <v>0.0025688614904308092</v>
       </c>
       <c r="R15">
-        <v>0.0026129263961873462</v>
+        <v>0.0025778947477879247</v>
       </c>
       <c r="S15">
-        <v>0.002483236785824447</v>
+        <v>0.0024596280268815128</v>
       </c>
       <c r="T15">
-        <v>0.0025682035418026893</v>
+        <v>0.0025364596713867097</v>
       </c>
       <c r="U15">
-        <v>0.0029105097729453947</v>
+        <v>0.0028697643524394664</v>
       </c>
       <c r="V15">
-        <v>0.0026523068570603946</v>
+        <v>0.0026181171871513236</v>
       </c>
       <c r="W15">
-        <v>0.0027302465707751749</v>
+        <v>0.0027003034586810283</v>
       </c>
       <c r="X15">
-        <v>0.0026625833312308761</v>
+        <v>0.0026283514772935807</v>
       </c>
       <c r="Y15">
-        <v>0.0026755642614487429</v>
+        <v>0.0026422633971703137</v>
       </c>
       <c r="Z15">
-        <v>6.562032427462767e-005</v>
+        <v>6.2827188494826898e-005</v>
       </c>
       <c r="AA15">
-        <v>-0.00045937939056366907</v>
+        <v>-0.00042333516315695702</v>
       </c>
       <c r="AB15">
-        <v>-0.00028713066148122068</v>
+        <v>-0.00019207311703131207</v>
       </c>
       <c r="AC15">
-        <v>0.00066126880849868663</v>
+        <v>0.00064891673791304147</v>
       </c>
       <c r="AD15">
-        <v>0.0037694255432193569</v>
+        <v>0.0037078822696152889</v>
       </c>
       <c r="AE15">
-        <v>0.00041677762801240771</v>
+        <v>0.00041027442714807431</v>
       </c>
       <c r="AF15">
-        <v>-0.0064443620420500608</v>
+        <v>-0.0064453537719234774</v>
       </c>
     </row>
     <row r="16">
@@ -1909,97 +1909,97 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>0.14365496576677064</v>
+        <v>0.16029198427979829</v>
       </c>
       <c r="C16">
-        <v>2.4286437325781278e-005</v>
+        <v>1.0584537154877346e-005</v>
       </c>
       <c r="D16">
-        <v>0.00030059032528016185</v>
+        <v>0.00033213247295246382</v>
       </c>
       <c r="E16">
-        <v>-5.8352262043271684e-006</v>
+        <v>-6.4208637660308852e-006</v>
       </c>
       <c r="F16">
-        <v>7.4826797288005749e-005</v>
+        <v>0.00012257753311536231</v>
       </c>
       <c r="G16">
-        <v>0.00021444698103237987</v>
+        <v>0.00023291613436434257</v>
       </c>
       <c r="H16">
-        <v>0.00032281677300110184</v>
+        <v>0.00032096454713878157</v>
       </c>
       <c r="I16">
-        <v>0.0001015586772983543</v>
+        <v>8.4685382186537551e-005</v>
       </c>
       <c r="J16">
-        <v>7.8046457099332253e-005</v>
+        <v>7.2347178632508366e-005</v>
       </c>
       <c r="K16">
-        <v>3.9284211488679432e-005</v>
+        <v>3.9354669028877128e-005</v>
       </c>
       <c r="L16">
-        <v>-1.4715983564685424e-005</v>
+        <v>-3.7503622150512569e-005</v>
       </c>
       <c r="M16">
-        <v>0.00033622633650817974</v>
+        <v>0.00032231913275913371</v>
       </c>
       <c r="N16">
-        <v>0.00032485661051898692</v>
+        <v>0.00029894130618722211</v>
       </c>
       <c r="O16">
-        <v>0.0026512963125486693</v>
+        <v>0.0026256451612013685</v>
       </c>
       <c r="P16">
-        <v>0.0026023254588194746</v>
+        <v>0.0025688614904308092</v>
       </c>
       <c r="Q16">
-        <v>0.0052110326516957989</v>
+        <v>0.0050702266362151515</v>
       </c>
       <c r="R16">
-        <v>0.0026527402576675793</v>
+        <v>0.0026225698166147155</v>
       </c>
       <c r="S16">
-        <v>0.0025068850893304744</v>
+        <v>0.0024888436038571632</v>
       </c>
       <c r="T16">
-        <v>0.0026190666960060828</v>
+        <v>0.0025897686854286519</v>
       </c>
       <c r="U16">
-        <v>0.0029583576247644164</v>
+        <v>0.002919328947956587</v>
       </c>
       <c r="V16">
-        <v>0.0027242279417533681</v>
+        <v>0.0026963545923479916</v>
       </c>
       <c r="W16">
-        <v>0.0027580181389388857</v>
+        <v>0.0027313241297134308</v>
       </c>
       <c r="X16">
-        <v>0.0027200123070793419</v>
+        <v>0.0026945492957706381</v>
       </c>
       <c r="Y16">
-        <v>0.0026850583421821703</v>
+        <v>0.0026484323624466908</v>
       </c>
       <c r="Z16">
-        <v>2.3675492226109989e-005</v>
+        <v>2.246368805858208e-005</v>
       </c>
       <c r="AA16">
-        <v>-0.00024592377842004012</v>
+        <v>-0.00024282462438062938</v>
       </c>
       <c r="AB16">
-        <v>0.000222279552238256</v>
+        <v>0.00020759784063241452</v>
       </c>
       <c r="AC16">
-        <v>0.00083193504082763555</v>
+        <v>0.00080616989676829387</v>
       </c>
       <c r="AD16">
-        <v>0.0038435037820535247</v>
+        <v>0.0037673529644965944</v>
       </c>
       <c r="AE16">
-        <v>0.00066866753885169749</v>
+        <v>0.00066304719259550286</v>
       </c>
       <c r="AF16">
-        <v>-0.0071908079855674207</v>
+        <v>-0.007538787676784591</v>
       </c>
     </row>
     <row r="17">
@@ -2007,97 +2007,97 @@
         <v>29</v>
       </c>
       <c r="B17">
-        <v>0.063793731169171475</v>
+        <v>0.068786874278628909</v>
       </c>
       <c r="C17">
-        <v>1.4892058278357213e-005</v>
+        <v>1.0874507537781872e-005</v>
       </c>
       <c r="D17">
-        <v>0.00021660237617516798</v>
+        <v>0.00024525505148135845</v>
       </c>
       <c r="E17">
-        <v>-4.2505075881772647e-006</v>
+        <v>-4.7740958425850572e-006</v>
       </c>
       <c r="F17">
-        <v>0.00019724069310306133</v>
+        <v>0.00021272113071302116</v>
       </c>
       <c r="G17">
-        <v>0.00019391979829262506</v>
+        <v>0.00020437215978698611</v>
       </c>
       <c r="H17">
-        <v>0.00027077130084104787</v>
+        <v>0.00024491604112460407</v>
       </c>
       <c r="I17">
-        <v>-7.8784182296940384e-005</v>
+        <v>-8.1775848537707352e-005</v>
       </c>
       <c r="J17">
-        <v>-0.00025891891098770456</v>
+        <v>-0.00022824039109469531</v>
       </c>
       <c r="K17">
-        <v>-0.00030452664278785962</v>
+        <v>-0.00026979754605460139</v>
       </c>
       <c r="L17">
-        <v>-0.00027995558856231442</v>
+        <v>-0.00026172850415994402</v>
       </c>
       <c r="M17">
-        <v>-0.0001212867631756516</v>
+        <v>-9.9778175767282963e-005</v>
       </c>
       <c r="N17">
-        <v>-0.00010201778916059867</v>
+        <v>-9.1208594492976126e-005</v>
       </c>
       <c r="O17">
-        <v>0.0026527326154781529</v>
+        <v>0.002624626502797591</v>
       </c>
       <c r="P17">
-        <v>0.0026129263961873462</v>
+        <v>0.0025778947477879247</v>
       </c>
       <c r="Q17">
-        <v>0.0026527402576675793</v>
+        <v>0.0026225698166147155</v>
       </c>
       <c r="R17">
-        <v>0.0052755410137377574</v>
+        <v>0.0051697186860243912</v>
       </c>
       <c r="S17">
-        <v>0.0025299950494819872</v>
+        <v>0.0025103699081951273</v>
       </c>
       <c r="T17">
-        <v>0.0026339004030856367</v>
+        <v>0.0026055996575288149</v>
       </c>
       <c r="U17">
-        <v>0.0030009404669813075</v>
+        <v>0.0029594832328360778</v>
       </c>
       <c r="V17">
-        <v>0.002745141438622201</v>
+        <v>0.0027170564470863387</v>
       </c>
       <c r="W17">
-        <v>0.0027732505949154104</v>
+        <v>0.0027446655793032372</v>
       </c>
       <c r="X17">
-        <v>0.0027094888860936519</v>
+        <v>0.0026816220525210112</v>
       </c>
       <c r="Y17">
-        <v>0.0027196330475743424</v>
+        <v>0.0026832672754183054</v>
       </c>
       <c r="Z17">
-        <v>1.8628122513745431e-005</v>
+        <v>1.8003032669549409e-005</v>
       </c>
       <c r="AA17">
-        <v>-7.5867145263683512e-005</v>
+        <v>-7.6591315358183116e-005</v>
       </c>
       <c r="AB17">
-        <v>-7.7112794471408152e-005</v>
+        <v>-8.6264400349683648e-005</v>
       </c>
       <c r="AC17">
-        <v>0.0008455155953252969</v>
+        <v>0.00081760394751968063</v>
       </c>
       <c r="AD17">
-        <v>0.0039129067942044321</v>
+        <v>0.0038455019985996655</v>
       </c>
       <c r="AE17">
-        <v>0.00056262206897762291</v>
+        <v>0.0005601594128802201</v>
       </c>
       <c r="AF17">
-        <v>-0.0056772332627614917</v>
+        <v>-0.0060338518062252227</v>
       </c>
     </row>
     <row r="18">
@@ -2105,97 +2105,97 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>0.021232055149430235</v>
+        <v>0.053215523672966322</v>
       </c>
       <c r="C18">
-        <v>4.6428926975511335e-005</v>
+        <v>5.9699405613395097e-005</v>
       </c>
       <c r="D18">
-        <v>0.0002079362161228125</v>
+        <v>0.00022247914151527284</v>
       </c>
       <c r="E18">
-        <v>-4.1798220484551469e-006</v>
+        <v>-4.4638876930843847e-006</v>
       </c>
       <c r="F18">
-        <v>3.0487714189990833e-005</v>
+        <v>1.068681583784605e-005</v>
       </c>
       <c r="G18">
-        <v>0.00025811460608230266</v>
+        <v>0.00023964805423711466</v>
       </c>
       <c r="H18">
-        <v>-5.277371719381637e-005</v>
+        <v>-8.2862081123117074e-005</v>
       </c>
       <c r="I18">
-        <v>-0.00017870944201391027</v>
+        <v>-0.00016426467398710821</v>
       </c>
       <c r="J18">
-        <v>-0.00011097770649574077</v>
+        <v>-0.00010352144696709341</v>
       </c>
       <c r="K18">
-        <v>-0.00028883730445634025</v>
+        <v>-0.00028655286503329156</v>
       </c>
       <c r="L18">
-        <v>-0.00017497526215940027</v>
+        <v>-0.00019962571270795313</v>
       </c>
       <c r="M18">
-        <v>-0.00011168416915693772</v>
+        <v>-0.00010914618536152806</v>
       </c>
       <c r="N18">
-        <v>3.4634591117102282e-006</v>
+        <v>-2.7246929796371708e-008</v>
       </c>
       <c r="O18">
-        <v>0.0024745579431253778</v>
+        <v>0.0024624398276962317</v>
       </c>
       <c r="P18">
-        <v>0.002483236785824447</v>
+        <v>0.0024596280268815128</v>
       </c>
       <c r="Q18">
-        <v>0.0025068850893304744</v>
+        <v>0.0024888436038571632</v>
       </c>
       <c r="R18">
-        <v>0.0025299950494819872</v>
+        <v>0.0025103699081951273</v>
       </c>
       <c r="S18">
-        <v>0.0056917455071367916</v>
+        <v>0.0054562262158130764</v>
       </c>
       <c r="T18">
-        <v>0.0024941829845446109</v>
+        <v>0.002479823341953498</v>
       </c>
       <c r="U18">
-        <v>0.0028486916069823225</v>
+        <v>0.0028164296991797207</v>
       </c>
       <c r="V18">
-        <v>0.0025713345998154328</v>
+        <v>0.0025560997751372444</v>
       </c>
       <c r="W18">
-        <v>0.0026239231717641786</v>
+        <v>0.0026073238171190386</v>
       </c>
       <c r="X18">
-        <v>0.0025541839119029466</v>
+        <v>0.0025381024809861211</v>
       </c>
       <c r="Y18">
-        <v>0.0025761426158675054</v>
+        <v>0.002554671048397893</v>
       </c>
       <c r="Z18">
-        <v>5.3771493390035246e-005</v>
+        <v>4.9072342301868322e-005</v>
       </c>
       <c r="AA18">
-        <v>-0.0004121844687430986</v>
+        <v>-0.00038404948452487288</v>
       </c>
       <c r="AB18">
-        <v>-0.00029361694012370525</v>
+        <v>-0.00027234036827243093</v>
       </c>
       <c r="AC18">
-        <v>0.00023525985564097228</v>
+        <v>0.00023603575976264017</v>
       </c>
       <c r="AD18">
-        <v>0.0037627366577099464</v>
+        <v>0.0037007543919348007</v>
       </c>
       <c r="AE18">
-        <v>0.00021752375765130114</v>
+        <v>0.00022952962553594164</v>
       </c>
       <c r="AF18">
-        <v>-0.0059732266861116674</v>
+        <v>-0.0060445062227189724</v>
       </c>
     </row>
     <row r="19">
@@ -2203,97 +2203,97 @@
         <v>31</v>
       </c>
       <c r="B19">
-        <v>0.02146076740971458</v>
+        <v>0.018853131291135843</v>
       </c>
       <c r="C19">
-        <v>-3.5958054796422462e-005</v>
+        <v>-3.1771608435001794e-005</v>
       </c>
       <c r="D19">
-        <v>0.00027631341562180079</v>
+        <v>0.00029151588484822421</v>
       </c>
       <c r="E19">
-        <v>-5.2013292076234029e-006</v>
+        <v>-5.5002422869261718e-006</v>
       </c>
       <c r="F19">
-        <v>-5.7998533885439461e-005</v>
+        <v>-4.8702772164874219e-005</v>
       </c>
       <c r="G19">
-        <v>0.00017318871733665943</v>
+        <v>0.00018255517519527977</v>
       </c>
       <c r="H19">
-        <v>-0.00018899969872881436</v>
+        <v>-0.00015866347838978619</v>
       </c>
       <c r="I19">
-        <v>0.00013078946834898001</v>
+        <v>0.00013280946826447722</v>
       </c>
       <c r="J19">
-        <v>9.2760294381045256e-005</v>
+        <v>9.410148428282551e-005</v>
       </c>
       <c r="K19">
-        <v>-8.2853231408423972e-005</v>
+        <v>-5.2620313204844677e-005</v>
       </c>
       <c r="L19">
-        <v>-0.00012738039146002414</v>
+        <v>-0.00012065154193495307</v>
       </c>
       <c r="M19">
-        <v>-8.183642104436274e-005</v>
+        <v>-5.0768722785341858e-005</v>
       </c>
       <c r="N19">
-        <v>0.00023011720666271608</v>
+        <v>0.00023897692962961202</v>
       </c>
       <c r="O19">
-        <v>0.0026114294380400502</v>
+        <v>0.0025855034717256606</v>
       </c>
       <c r="P19">
-        <v>0.0025682035418026893</v>
+        <v>0.0025364596713867097</v>
       </c>
       <c r="Q19">
-        <v>0.0026190666960060828</v>
+        <v>0.0025897686854286519</v>
       </c>
       <c r="R19">
-        <v>0.0026339004030856367</v>
+        <v>0.0026055996575288149</v>
       </c>
       <c r="S19">
-        <v>0.0024941829845446109</v>
+        <v>0.002479823341953498</v>
       </c>
       <c r="T19">
-        <v>0.0052372968075392297</v>
+        <v>0.0051375655572381464</v>
       </c>
       <c r="U19">
-        <v>0.0029392159262557906</v>
+        <v>0.0029060138536134584</v>
       </c>
       <c r="V19">
-        <v>0.0027355208377856277</v>
+        <v>0.0027048485621034616</v>
       </c>
       <c r="W19">
-        <v>0.0027519615000695836</v>
+        <v>0.0027213651129129129</v>
       </c>
       <c r="X19">
-        <v>0.0027040994764396475</v>
+        <v>0.0026750172004596025</v>
       </c>
       <c r="Y19">
-        <v>0.0027081533904141156</v>
+        <v>0.0026708983741685448</v>
       </c>
       <c r="Z19">
-        <v>1.4753767570633951e-005</v>
+        <v>1.5106799700607574e-005</v>
       </c>
       <c r="AA19">
-        <v>-8.506071955861014e-005</v>
+        <v>-9.2020964525844261e-005</v>
       </c>
       <c r="AB19">
-        <v>1.6539326557960996e-005</v>
+        <v>2.308189150632405e-006</v>
       </c>
       <c r="AC19">
-        <v>0.00089916197048965174</v>
+        <v>0.00085620122231748312</v>
       </c>
       <c r="AD19">
-        <v>0.0035529956773206932</v>
+        <v>0.0034918990804817633</v>
       </c>
       <c r="AE19">
-        <v>0.0004763512895334504</v>
+        <v>0.00046633034542556748</v>
       </c>
       <c r="AF19">
-        <v>-0.0065910688546137238</v>
+        <v>-0.0067712057912613201</v>
       </c>
     </row>
     <row r="20">
@@ -2301,97 +2301,97 @@
         <v>32</v>
       </c>
       <c r="B20">
-        <v>-0.024044419884632032</v>
+        <v>-0.0038043083291995228</v>
       </c>
       <c r="C20">
-        <v>-4.1301744140845342e-005</v>
+        <v>-5.1570223737230764e-005</v>
       </c>
       <c r="D20">
-        <v>0.00019166427248898388</v>
+        <v>0.00022378493367959489</v>
       </c>
       <c r="E20">
-        <v>-3.8649835366198458e-006</v>
+        <v>-4.4404589689473254e-006</v>
       </c>
       <c r="F20">
-        <v>0.00031801106009928274</v>
+        <v>0.00034230433020416206</v>
       </c>
       <c r="G20">
-        <v>0.00043702534909603069</v>
+        <v>0.00043970249710389661</v>
       </c>
       <c r="H20">
-        <v>0.00018180829151978953</v>
+        <v>0.00020045470572709187</v>
       </c>
       <c r="I20">
-        <v>-0.00020251013834823297</v>
+        <v>-0.00019874842424609475</v>
       </c>
       <c r="J20">
-        <v>-2.2676695775995966e-005</v>
+        <v>-2.9382869025809319e-005</v>
       </c>
       <c r="K20">
-        <v>-0.00011272713776758572</v>
+        <v>-0.00010007578409842901</v>
       </c>
       <c r="L20">
-        <v>-0.00019477596782150491</v>
+        <v>-0.00018710133741960686</v>
       </c>
       <c r="M20">
-        <v>0.00019276706255083229</v>
+        <v>0.00018623961052561676</v>
       </c>
       <c r="N20">
-        <v>5.244897218382831e-005</v>
+        <v>4.0710872103126919e-005</v>
       </c>
       <c r="O20">
-        <v>0.0030277306313199106</v>
+        <v>0.0029859753387207933</v>
       </c>
       <c r="P20">
-        <v>0.0029105097729453947</v>
+        <v>0.0028697643524394664</v>
       </c>
       <c r="Q20">
-        <v>0.0029583576247644164</v>
+        <v>0.002919328947956587</v>
       </c>
       <c r="R20">
-        <v>0.0030009404669813075</v>
+        <v>0.0029594832328360778</v>
       </c>
       <c r="S20">
-        <v>0.0028486916069823225</v>
+        <v>0.0028164296991797207</v>
       </c>
       <c r="T20">
-        <v>0.0029392159262557906</v>
+        <v>0.0029060138536134584</v>
       </c>
       <c r="U20">
-        <v>0.005423794839862957</v>
+        <v>0.0052830573762295057</v>
       </c>
       <c r="V20">
-        <v>0.0030876605555813295</v>
+        <v>0.0030461831173824805</v>
       </c>
       <c r="W20">
-        <v>0.0031421363768925461</v>
+        <v>0.0031010174273135818</v>
       </c>
       <c r="X20">
-        <v>0.0031065757746753775</v>
+        <v>0.0030635706954029668</v>
       </c>
       <c r="Y20">
-        <v>0.003117484075616299</v>
+        <v>0.0030660385396002934</v>
       </c>
       <c r="Z20">
-        <v>4.6122241383832847e-005</v>
+        <v>4.278207868821588e-005</v>
       </c>
       <c r="AA20">
-        <v>-0.00034632086997093156</v>
+        <v>-0.00031570827992504543</v>
       </c>
       <c r="AB20">
-        <v>-0.00025353831651395186</v>
+        <v>-0.00024902419424696219</v>
       </c>
       <c r="AC20">
-        <v>0.0010528781616053484</v>
+        <v>0.0010130821971961975</v>
       </c>
       <c r="AD20">
-        <v>0.006399662749753449</v>
+        <v>0.0062246576671145734</v>
       </c>
       <c r="AE20">
-        <v>0.00070015276382089011</v>
+        <v>0.00069089281090230713</v>
       </c>
       <c r="AF20">
-        <v>-0.0064171610485045929</v>
+        <v>-0.0067438437145954881</v>
       </c>
     </row>
     <row r="21">
@@ -2399,97 +2399,97 @@
         <v>33</v>
       </c>
       <c r="B21">
-        <v>0.1894636562594465</v>
+        <v>0.18863688864436348</v>
       </c>
       <c r="C21">
-        <v>3.6187792571575235e-005</v>
+        <v>4.1294202976552261e-005</v>
       </c>
       <c r="D21">
-        <v>0.00023579903342900725</v>
+        <v>0.00028890468513969735</v>
       </c>
       <c r="E21">
-        <v>-4.5594647668786777e-006</v>
+        <v>-5.5117995684629683e-006</v>
       </c>
       <c r="F21">
-        <v>-5.1069468318189616e-005</v>
+        <v>-1.9939031848869313e-005</v>
       </c>
       <c r="G21">
-        <v>0.00011673572119270763</v>
+        <v>0.00011515613050978781</v>
       </c>
       <c r="H21">
-        <v>9.460330328559945e-005</v>
+        <v>8.460444925412696e-005</v>
       </c>
       <c r="I21">
-        <v>3.1072259535607567e-005</v>
+        <v>0.00010485499664486639</v>
       </c>
       <c r="J21">
-        <v>-0.00010739347382454037</v>
+        <v>8.9401227001010891e-006</v>
       </c>
       <c r="K21">
-        <v>-1.6199263216596684e-005</v>
+        <v>0.00010283148016374758</v>
       </c>
       <c r="L21">
-        <v>-0.00010281932410645725</v>
+        <v>-3.8076447667331e-005</v>
       </c>
       <c r="M21">
-        <v>4.630706637586161e-007</v>
+        <v>0.00010554757078274897</v>
       </c>
       <c r="N21">
-        <v>4.9712087249859072e-005</v>
+        <v>0.00012970008258914338</v>
       </c>
       <c r="O21">
-        <v>0.0027502628493991052</v>
+        <v>0.0027176783579206539</v>
       </c>
       <c r="P21">
-        <v>0.0026523068570603946</v>
+        <v>0.0026181171871513236</v>
       </c>
       <c r="Q21">
-        <v>0.0027242279417533681</v>
+        <v>0.0026963545923479916</v>
       </c>
       <c r="R21">
-        <v>0.002745141438622201</v>
+        <v>0.0027170564470863387</v>
       </c>
       <c r="S21">
-        <v>0.0025713345998154328</v>
+        <v>0.0025560997751372444</v>
       </c>
       <c r="T21">
-        <v>0.0027355208377856277</v>
+        <v>0.0027048485621034616</v>
       </c>
       <c r="U21">
-        <v>0.0030876605555813295</v>
+        <v>0.0030461831173824805</v>
       </c>
       <c r="V21">
-        <v>0.0057696896366964791</v>
+        <v>0.0057064119395707404</v>
       </c>
       <c r="W21">
-        <v>0.0028570989346373321</v>
+        <v>0.0028259233744568034</v>
       </c>
       <c r="X21">
-        <v>0.0028371211610437952</v>
+        <v>0.0028051674696313498</v>
       </c>
       <c r="Y21">
-        <v>0.0028117398393861489</v>
+        <v>0.0027722830852368349</v>
       </c>
       <c r="Z21">
-        <v>2.1265308766649043e-005</v>
+        <v>2.2936764694630736e-005</v>
       </c>
       <c r="AA21">
-        <v>-0.00014654669975962606</v>
+        <v>-0.00014000460067919849</v>
       </c>
       <c r="AB21">
-        <v>0.00017354956495369114</v>
+        <v>9.220092520512385e-005</v>
       </c>
       <c r="AC21">
-        <v>0.0010192537959087982</v>
+        <v>0.00097741732400680702</v>
       </c>
       <c r="AD21">
-        <v>0.0041395571462687995</v>
+        <v>0.0040540843389370966</v>
       </c>
       <c r="AE21">
-        <v>0.00087271599260421956</v>
+        <v>0.00085145815746772986</v>
       </c>
       <c r="AF21">
-        <v>-0.0062129698122974</v>
+        <v>-0.0070156974466466914</v>
       </c>
     </row>
     <row r="22">
@@ -2497,97 +2497,97 @@
         <v>34</v>
       </c>
       <c r="B22">
-        <v>-0.0051673958431578586</v>
+        <v>-0.010326579922950359</v>
       </c>
       <c r="C22">
-        <v>-1.7544118655730776e-005</v>
+        <v>-1.5039910363546828e-005</v>
       </c>
       <c r="D22">
-        <v>0.00017986352000253186</v>
+        <v>0.00021055904214598411</v>
       </c>
       <c r="E22">
-        <v>-3.7516276753519595e-006</v>
+        <v>-4.3484124492790248e-006</v>
       </c>
       <c r="F22">
-        <v>9.3417537433968575e-006</v>
+        <v>4.4493988832149459e-005</v>
       </c>
       <c r="G22">
-        <v>0.00021077573410292836</v>
+        <v>0.00023546423936156432</v>
       </c>
       <c r="H22">
-        <v>-0.00029061778133209826</v>
+        <v>-0.00027289333462918424</v>
       </c>
       <c r="I22">
-        <v>-1.0386168376098253e-005</v>
+        <v>-1.9790987203760577e-005</v>
       </c>
       <c r="J22">
-        <v>-2.2264799040716326e-005</v>
+        <v>-2.159535163679554e-005</v>
       </c>
       <c r="K22">
-        <v>-0.00029733774912710166</v>
+        <v>-0.00027214372833735362</v>
       </c>
       <c r="L22">
-        <v>-0.00014030637654814551</v>
+        <v>-0.00014170826613530666</v>
       </c>
       <c r="M22">
-        <v>0.00020039211946581764</v>
+        <v>0.00022004732524477416</v>
       </c>
       <c r="N22">
-        <v>0.00017063826866511736</v>
+        <v>0.0001632664983259079</v>
       </c>
       <c r="O22">
-        <v>0.0027541630446469298</v>
+        <v>0.0027274676973273854</v>
       </c>
       <c r="P22">
-        <v>0.0027302465707751749</v>
+        <v>0.0027003034586810283</v>
       </c>
       <c r="Q22">
-        <v>0.0027580181389388857</v>
+        <v>0.0027313241297134308</v>
       </c>
       <c r="R22">
-        <v>0.0027732505949154104</v>
+        <v>0.0027446655793032372</v>
       </c>
       <c r="S22">
-        <v>0.0026239231717641786</v>
+        <v>0.0026073238171190386</v>
       </c>
       <c r="T22">
-        <v>0.0027519615000695836</v>
+        <v>0.0027213651129129129</v>
       </c>
       <c r="U22">
-        <v>0.0031421363768925461</v>
+        <v>0.0031010174273135818</v>
       </c>
       <c r="V22">
-        <v>0.0028570989346373321</v>
+        <v>0.0028259233744568034</v>
       </c>
       <c r="W22">
-        <v>0.0065645153608101196</v>
+        <v>0.0064786314206326488</v>
       </c>
       <c r="X22">
-        <v>0.0028159385578555643</v>
+        <v>0.002791483574670052</v>
       </c>
       <c r="Y22">
-        <v>0.0028855938898864784</v>
+        <v>0.0028506044108713583</v>
       </c>
       <c r="Z22">
-        <v>3.6619931954998521e-005</v>
+        <v>3.4645424818555745e-005</v>
       </c>
       <c r="AA22">
-        <v>-0.00028844895466436846</v>
+        <v>-0.00025834032404684933</v>
       </c>
       <c r="AB22">
-        <v>-5.2360169187249815e-005</v>
+        <v>-5.6721182092902037e-005</v>
       </c>
       <c r="AC22">
-        <v>0.0010235420451779663</v>
+        <v>0.0010001953792593316</v>
       </c>
       <c r="AD22">
-        <v>0.004292028419354707</v>
+        <v>0.004227232044407842</v>
       </c>
       <c r="AE22">
-        <v>0.0007798203814307819</v>
+        <v>0.000790384155859607</v>
       </c>
       <c r="AF22">
-        <v>-0.0056687295865195742</v>
+        <v>-0.0060112535132983572</v>
       </c>
     </row>
     <row r="23">
@@ -2595,97 +2595,97 @@
         <v>35</v>
       </c>
       <c r="B23">
-        <v>0.1068743735080132</v>
+        <v>0.12724499658639871</v>
       </c>
       <c r="C23">
-        <v>-2.276573461783743e-005</v>
+        <v>-1.4977656740259843e-005</v>
       </c>
       <c r="D23">
-        <v>0.00039292329618259461</v>
+        <v>0.00040755150323139224</v>
       </c>
       <c r="E23">
-        <v>-7.05062464731388e-006</v>
+        <v>-7.378021292163009e-006</v>
       </c>
       <c r="F23">
-        <v>0.0004424192836913909</v>
+        <v>0.00048886398706520222</v>
       </c>
       <c r="G23">
-        <v>0.00047431797428717907</v>
+        <v>0.00046663588295321756</v>
       </c>
       <c r="H23">
-        <v>0.00025288903893850879</v>
+        <v>0.00025721441367772046</v>
       </c>
       <c r="I23">
-        <v>-0.00043857718608658841</v>
+        <v>-0.00043595354744736564</v>
       </c>
       <c r="J23">
-        <v>-0.00032945400874874464</v>
+        <v>-0.00030335970941101518</v>
       </c>
       <c r="K23">
-        <v>0.00010930006450980787</v>
+        <v>0.00010489516307815301</v>
       </c>
       <c r="L23">
-        <v>-0.00043012428892554976</v>
+        <v>-0.00042082317678292485</v>
       </c>
       <c r="M23">
-        <v>-0.00020713612021222409</v>
+        <v>-0.00017493195207135017</v>
       </c>
       <c r="N23">
-        <v>-0.00019682366098021039</v>
+        <v>-0.00019104519575067233</v>
       </c>
       <c r="O23">
-        <v>0.0027103462515041367</v>
+        <v>0.0026847055323007433</v>
       </c>
       <c r="P23">
-        <v>0.0026625833312308761</v>
+        <v>0.0026283514772935807</v>
       </c>
       <c r="Q23">
-        <v>0.0027200123070793419</v>
+        <v>0.0026945492957706381</v>
       </c>
       <c r="R23">
-        <v>0.0027094888860936519</v>
+        <v>0.0026816220525210112</v>
       </c>
       <c r="S23">
-        <v>0.0025541839119029466</v>
+        <v>0.0025381024809861211</v>
       </c>
       <c r="T23">
-        <v>0.0027040994764396475</v>
+        <v>0.0026750172004596025</v>
       </c>
       <c r="U23">
-        <v>0.0031065757746753775</v>
+        <v>0.0030635706954029668</v>
       </c>
       <c r="V23">
-        <v>0.0028371211610437952</v>
+        <v>0.0028051674696313498</v>
       </c>
       <c r="W23">
-        <v>0.0028159385578555643</v>
+        <v>0.002791483574670052</v>
       </c>
       <c r="X23">
-        <v>0.0059601453710931883</v>
+        <v>0.0058121901559382147</v>
       </c>
       <c r="Y23">
-        <v>0.00279745933204361</v>
+        <v>0.0027627597068258561</v>
       </c>
       <c r="Z23">
-        <v>4.996522195110459e-005</v>
+        <v>4.673916043484072e-005</v>
       </c>
       <c r="AA23">
-        <v>-0.00032692067955440729</v>
+        <v>-0.00027368782160687633</v>
       </c>
       <c r="AB23">
-        <v>-0.0001967838209606743</v>
+        <v>-0.00018939535630619155</v>
       </c>
       <c r="AC23">
-        <v>0.0010073955511555699</v>
+        <v>0.00097691360025171578</v>
       </c>
       <c r="AD23">
-        <v>0.004127985227039224</v>
+        <v>0.0040626064447288196</v>
       </c>
       <c r="AE23">
-        <v>0.0006491054737402446</v>
+        <v>0.00062913858855751697</v>
       </c>
       <c r="AF23">
-        <v>-0.0089471025665843751</v>
+        <v>-0.0090350103890579937</v>
       </c>
     </row>
     <row r="24">
@@ -2693,97 +2693,97 @@
         <v>36</v>
       </c>
       <c r="B24">
-        <v>-0.10982553431714658</v>
+        <v>-0.12941144766228069</v>
       </c>
       <c r="C24">
-        <v>6.5013478474758725e-005</v>
+        <v>6.0594841515417539e-005</v>
       </c>
       <c r="D24">
-        <v>7.063291650684627e-005</v>
+        <v>8.9189338162662737e-005</v>
       </c>
       <c r="E24">
-        <v>-1.6139807609959894e-006</v>
+        <v>-1.9618617589507151e-006</v>
       </c>
       <c r="F24">
-        <v>-2.4534220518027117e-007</v>
+        <v>3.0788493923608086e-005</v>
       </c>
       <c r="G24">
-        <v>0.00026229625072693571</v>
+        <v>0.00027453127911696842</v>
       </c>
       <c r="H24">
-        <v>-0.00017878376142649441</v>
+        <v>-0.00015137127251240085</v>
       </c>
       <c r="I24">
-        <v>-3.0225521183643161e-005</v>
+        <v>-4.569076716493068e-005</v>
       </c>
       <c r="J24">
-        <v>-5.7069399919435979e-005</v>
+        <v>-4.8778623024560951e-005</v>
       </c>
       <c r="K24">
-        <v>-4.8141479433951549e-005</v>
+        <v>-3.0747806066477694e-005</v>
       </c>
       <c r="L24">
-        <v>-5.7485889338725407e-005</v>
+        <v>-7.0070697932111611e-005</v>
       </c>
       <c r="M24">
-        <v>0.0001459941279289478</v>
+        <v>0.00015378535548162507</v>
       </c>
       <c r="N24">
-        <v>0.00020044876780360259</v>
+        <v>0.00017950162568103768</v>
       </c>
       <c r="O24">
-        <v>0.0027503890877909063</v>
+        <v>0.002715518534505136</v>
       </c>
       <c r="P24">
-        <v>0.0026755642614487429</v>
+        <v>0.0026422633971703137</v>
       </c>
       <c r="Q24">
-        <v>0.0026850583421821703</v>
+        <v>0.0026484323624466908</v>
       </c>
       <c r="R24">
-        <v>0.0027196330475743424</v>
+        <v>0.0026832672754183054</v>
       </c>
       <c r="S24">
-        <v>0.0025761426158675054</v>
+        <v>0.002554671048397893</v>
       </c>
       <c r="T24">
-        <v>0.0027081533904141156</v>
+        <v>0.0026708983741685448</v>
       </c>
       <c r="U24">
-        <v>0.003117484075616299</v>
+        <v>0.0030660385396002934</v>
       </c>
       <c r="V24">
-        <v>0.0028117398393861489</v>
+        <v>0.0027722830852368349</v>
       </c>
       <c r="W24">
-        <v>0.0028855938898864784</v>
+        <v>0.0028506044108713583</v>
       </c>
       <c r="X24">
-        <v>0.00279745933204361</v>
+        <v>0.0027627597068258561</v>
       </c>
       <c r="Y24">
-        <v>0.0054876443880811148</v>
+        <v>0.0054580068535017246</v>
       </c>
       <c r="Z24">
-        <v>1.7019852293351733e-005</v>
+        <v>1.7385506305665711e-005</v>
       </c>
       <c r="AA24">
-        <v>-0.0002718363614222274</v>
+        <v>-0.00025329192613380614</v>
       </c>
       <c r="AB24">
-        <v>-0.00012462468550599476</v>
+        <v>-0.00014105978441622061</v>
       </c>
       <c r="AC24">
-        <v>0.0011215713986126171</v>
+        <v>0.0010854516708666087</v>
       </c>
       <c r="AD24">
-        <v>0.004277809101152729</v>
+        <v>0.0041961266474661359</v>
       </c>
       <c r="AE24">
-        <v>0.00075300304495632743</v>
+        <v>0.00072922057288449813</v>
       </c>
       <c r="AF24">
-        <v>-0.0040503102255273742</v>
+        <v>-0.0042619176919000438</v>
       </c>
     </row>
     <row r="25">
@@ -2791,97 +2791,97 @@
         <v>37</v>
       </c>
       <c r="B25">
-        <v>-0.013341251148365605</v>
+        <v>-0.014739123620402528</v>
       </c>
       <c r="C25">
-        <v>1.3427259276957812e-006</v>
+        <v>6.5302543672525151e-007</v>
       </c>
       <c r="D25">
-        <v>6.2381489539134298e-006</v>
+        <v>5.5465381527748832e-006</v>
       </c>
       <c r="E25">
-        <v>-1.1663576159463862e-007</v>
+        <v>-1.0277630215341281e-007</v>
       </c>
       <c r="F25">
-        <v>5.4229481479521656e-005</v>
+        <v>5.1608625830742451e-005</v>
       </c>
       <c r="G25">
-        <v>3.2268393460251261e-005</v>
+        <v>2.9394776555972057e-005</v>
       </c>
       <c r="H25">
-        <v>6.6193986219103542e-006</v>
+        <v>2.8983402962123091e-006</v>
       </c>
       <c r="I25">
-        <v>-4.1365468926742727e-005</v>
+        <v>-3.7555828676394745e-005</v>
       </c>
       <c r="J25">
-        <v>-2.7516889140124373e-005</v>
+        <v>-2.2044062251088108e-005</v>
       </c>
       <c r="K25">
-        <v>-6.9384629440293099e-006</v>
+        <v>-2.3510275671065209e-006</v>
       </c>
       <c r="L25">
-        <v>-1.34778923736856e-005</v>
+        <v>-1.053029378086435e-005</v>
       </c>
       <c r="M25">
-        <v>2.4024028695788244e-006</v>
+        <v>6.5363914788635607e-006</v>
       </c>
       <c r="N25">
-        <v>-2.8348228349493266e-005</v>
+        <v>-2.3723803880397378e-005</v>
       </c>
       <c r="O25">
-        <v>5.4844656493688369e-005</v>
+        <v>5.1592949014426793e-005</v>
       </c>
       <c r="P25">
-        <v>6.562032427462767e-005</v>
+        <v>6.2827188494826898e-005</v>
       </c>
       <c r="Q25">
-        <v>2.3675492226109989e-005</v>
+        <v>2.246368805858208e-005</v>
       </c>
       <c r="R25">
-        <v>1.8628122513745431e-005</v>
+        <v>1.8003032669549409e-005</v>
       </c>
       <c r="S25">
-        <v>5.3771493390035246e-005</v>
+        <v>4.9072342301868322e-005</v>
       </c>
       <c r="T25">
-        <v>1.4753767570633951e-005</v>
+        <v>1.5106799700607574e-005</v>
       </c>
       <c r="U25">
-        <v>4.6122241383832847e-005</v>
+        <v>4.278207868821588e-005</v>
       </c>
       <c r="V25">
-        <v>2.1265308766649043e-005</v>
+        <v>2.2936764694630736e-005</v>
       </c>
       <c r="W25">
-        <v>3.6619931954998521e-005</v>
+        <v>3.4645424818555745e-005</v>
       </c>
       <c r="X25">
-        <v>4.996522195110459e-005</v>
+        <v>4.673916043484072e-005</v>
       </c>
       <c r="Y25">
-        <v>1.7019852293351733e-005</v>
+        <v>1.7385506305665711e-005</v>
       </c>
       <c r="Z25">
-        <v>2.528983673771693e-005</v>
+        <v>2.4431235563151115e-005</v>
       </c>
       <c r="AA25">
-        <v>-0.00011033837155093996</v>
+        <v>-0.0001066875328638695</v>
       </c>
       <c r="AB25">
-        <v>-0.00013183146818149756</v>
+        <v>-0.00012822588938416545</v>
       </c>
       <c r="AC25">
-        <v>-2.4013365307961102e-005</v>
+        <v>-2.1917991800439777e-005</v>
       </c>
       <c r="AD25">
-        <v>0.00016748782875833693</v>
+        <v>0.00016061840862529377</v>
       </c>
       <c r="AE25">
-        <v>-3.2374072420371931e-005</v>
+        <v>-3.0810460231410312e-005</v>
       </c>
       <c r="AF25">
-        <v>-0.00051834020972574475</v>
+        <v>-0.0004969047454233944</v>
       </c>
     </row>
     <row r="26">
@@ -2889,97 +2889,97 @@
         <v>38</v>
       </c>
       <c r="B26">
-        <v>0.11956369144195139</v>
+        <v>0.11020020000248419</v>
       </c>
       <c r="C26">
-        <v>3.7105333980688243e-005</v>
+        <v>4.3492316941387736e-005</v>
       </c>
       <c r="D26">
-        <v>1.7416438658738562e-005</v>
+        <v>-1.7573168729699581e-006</v>
       </c>
       <c r="E26">
-        <v>-3.5598869384956496e-007</v>
+        <v>-1.9788895121810917e-008</v>
       </c>
       <c r="F26">
-        <v>2.3277202756666512e-005</v>
+        <v>-1.1134448375686896e-005</v>
       </c>
       <c r="G26">
-        <v>-0.00015900841811044463</v>
+        <v>-0.00014976418133005764</v>
       </c>
       <c r="H26">
-        <v>7.0332452522272465e-005</v>
+        <v>8.1238770249010377e-005</v>
       </c>
       <c r="I26">
-        <v>-0.00011250905909482908</v>
+        <v>-8.6283811761349058e-005</v>
       </c>
       <c r="J26">
-        <v>-0.00012532430826556602</v>
+        <v>-0.00013068494898034382</v>
       </c>
       <c r="K26">
-        <v>-0.00014738160509518758</v>
+        <v>-0.00015745810876441126</v>
       </c>
       <c r="L26">
-        <v>-0.00018271531471755498</v>
+        <v>-0.0001626795232896356</v>
       </c>
       <c r="M26">
-        <v>-0.00021619057127154258</v>
+        <v>-0.00020573075219414654</v>
       </c>
       <c r="N26">
-        <v>-0.00019430985241639744</v>
+        <v>-0.00021449840702193014</v>
       </c>
       <c r="O26">
-        <v>-0.00038748566674939834</v>
+        <v>-0.00035310705837768194</v>
       </c>
       <c r="P26">
-        <v>-0.00045937939056366907</v>
+        <v>-0.00042333516315695702</v>
       </c>
       <c r="Q26">
-        <v>-0.00024592377842004012</v>
+        <v>-0.00024282462438062938</v>
       </c>
       <c r="R26">
-        <v>-7.5867145263683512e-005</v>
+        <v>-7.6591315358183116e-005</v>
       </c>
       <c r="S26">
-        <v>-0.0004121844687430986</v>
+        <v>-0.00038404948452487288</v>
       </c>
       <c r="T26">
-        <v>-8.506071955861014e-005</v>
+        <v>-9.2020964525844261e-005</v>
       </c>
       <c r="U26">
-        <v>-0.00034632086997093156</v>
+        <v>-0.00031570827992504543</v>
       </c>
       <c r="V26">
-        <v>-0.00014654669975962606</v>
+        <v>-0.00014000460067919849</v>
       </c>
       <c r="W26">
-        <v>-0.00028844895466436846</v>
+        <v>-0.00025834032404684933</v>
       </c>
       <c r="X26">
-        <v>-0.00032692067955440729</v>
+        <v>-0.00027368782160687633</v>
       </c>
       <c r="Y26">
-        <v>-0.0002718363614222274</v>
+        <v>-0.00025329192613380614</v>
       </c>
       <c r="Z26">
-        <v>-0.00011033837155093996</v>
+        <v>-0.0001066875328638695</v>
       </c>
       <c r="AA26">
-        <v>0.0040315412961126392</v>
+        <v>0.0040066930871553927</v>
       </c>
       <c r="AB26">
-        <v>0.00081316093311090804</v>
+        <v>0.00079538159568236135</v>
       </c>
       <c r="AC26">
-        <v>-2.1311338670532576e-005</v>
+        <v>-1.4349466299931699e-005</v>
       </c>
       <c r="AD26">
-        <v>-0.00097782986556344811</v>
+        <v>-0.00090025848297930772</v>
       </c>
       <c r="AE26">
-        <v>0.00076269541064717173</v>
+        <v>0.00081312700733148055</v>
       </c>
       <c r="AF26">
-        <v>0.0017880003694124883</v>
+        <v>0.0019630668412878266</v>
       </c>
     </row>
     <row r="27">
@@ -2987,97 +2987,97 @@
         <v>39</v>
       </c>
       <c r="B27">
-        <v>0.093634329426012561</v>
+        <v>0.084344972357574335</v>
       </c>
       <c r="C27">
-        <v>3.37528032464147e-005</v>
+        <v>2.1021733859948034e-005</v>
       </c>
       <c r="D27">
-        <v>-4.1134174872534601e-005</v>
+        <v>-4.672633855315857e-005</v>
       </c>
       <c r="E27">
-        <v>6.001557713089116e-007</v>
+        <v>6.4379934628539128e-007</v>
       </c>
       <c r="F27">
-        <v>-4.2837285484760611e-005</v>
+        <v>-4.3743892798587506e-005</v>
       </c>
       <c r="G27">
-        <v>-7.3833880595032368e-005</v>
+        <v>-5.0201176582674524e-005</v>
       </c>
       <c r="H27">
-        <v>-4.0582446417701252e-005</v>
+        <v>-2.0613297126215776e-005</v>
       </c>
       <c r="I27">
-        <v>4.9325869880878287e-005</v>
+        <v>2.1894137232975801e-005</v>
       </c>
       <c r="J27">
-        <v>6.6643847136751066e-005</v>
+        <v>2.8965319935750247e-005</v>
       </c>
       <c r="K27">
-        <v>2.7648801358822958e-006</v>
+        <v>-2.7678162264313804e-005</v>
       </c>
       <c r="L27">
-        <v>0.00011944581315777194</v>
+        <v>0.00013111708089886599</v>
       </c>
       <c r="M27">
-        <v>0.00011150563132992673</v>
+        <v>7.5137056719524662e-005</v>
       </c>
       <c r="N27">
-        <v>0.00017872220122624669</v>
+        <v>0.00015369927807691109</v>
       </c>
       <c r="O27">
-        <v>-0.00036873138116462343</v>
+        <v>-0.00034395539638527872</v>
       </c>
       <c r="P27">
-        <v>-0.00028713066148122068</v>
+        <v>-0.00019207311703131207</v>
       </c>
       <c r="Q27">
-        <v>0.000222279552238256</v>
+        <v>0.00020759784063241452</v>
       </c>
       <c r="R27">
-        <v>-7.7112794471408152e-005</v>
+        <v>-8.6264400349683648e-005</v>
       </c>
       <c r="S27">
-        <v>-0.00029361694012370525</v>
+        <v>-0.00027234036827243093</v>
       </c>
       <c r="T27">
-        <v>1.6539326557960996e-005</v>
+        <v>2.308189150632405e-006</v>
       </c>
       <c r="U27">
-        <v>-0.00025353831651395186</v>
+        <v>-0.00024902419424696219</v>
       </c>
       <c r="V27">
-        <v>0.00017354956495369114</v>
+        <v>9.220092520512385e-005</v>
       </c>
       <c r="W27">
-        <v>-5.2360169187249815e-005</v>
+        <v>-5.6721182092902037e-005</v>
       </c>
       <c r="X27">
-        <v>-0.0001967838209606743</v>
+        <v>-0.00018939535630619155</v>
       </c>
       <c r="Y27">
-        <v>-0.00012462468550599476</v>
+        <v>-0.00014105978441622061</v>
       </c>
       <c r="Z27">
-        <v>-0.00013183146818149756</v>
+        <v>-0.00012822588938416545</v>
       </c>
       <c r="AA27">
-        <v>0.00081316093311090804</v>
+        <v>0.00079538159568236135</v>
       </c>
       <c r="AB27">
-        <v>0.0044056437068566937</v>
+        <v>0.004457779425538484</v>
       </c>
       <c r="AC27">
-        <v>4.5554320765456031e-005</v>
+        <v>3.7629052355877407e-005</v>
       </c>
       <c r="AD27">
-        <v>-0.00087718955161898856</v>
+        <v>-0.00087583067108481063</v>
       </c>
       <c r="AE27">
-        <v>9.330083940996896e-005</v>
+        <v>5.7965814224204842e-005</v>
       </c>
       <c r="AF27">
-        <v>0.0025096001777446314</v>
+        <v>0.0025807902245204772</v>
       </c>
     </row>
     <row r="28">
@@ -3085,97 +3085,97 @@
         <v>40</v>
       </c>
       <c r="B28">
-        <v>-0.46265329343749872</v>
+        <v>-0.4798228252780507</v>
       </c>
       <c r="C28">
-        <v>-1.9904845906785703e-005</v>
+        <v>-2.0599383813811514e-005</v>
       </c>
       <c r="D28">
-        <v>-5.7744566046178877e-005</v>
+        <v>-5.1421144777178372e-005</v>
       </c>
       <c r="E28">
-        <v>8.9701446253503958e-007</v>
+        <v>7.8005903958221288e-007</v>
       </c>
       <c r="F28">
-        <v>-5.9713529081658126e-006</v>
+        <v>1.2690773982487573e-005</v>
       </c>
       <c r="G28">
-        <v>0.00031586741325373684</v>
+        <v>0.00032553682570858221</v>
       </c>
       <c r="H28">
-        <v>0.00047216564744282622</v>
+        <v>0.0004793425591367354</v>
       </c>
       <c r="I28">
-        <v>0.00026098310407256589</v>
+        <v>0.00024296540258966423</v>
       </c>
       <c r="J28">
-        <v>0.00013984009935072515</v>
+        <v>0.00011857043577067228</v>
       </c>
       <c r="K28">
-        <v>0.0002051387955296774</v>
+        <v>0.00019642548064529577</v>
       </c>
       <c r="L28">
-        <v>0.00030886337408375479</v>
+        <v>0.00028942878634061371</v>
       </c>
       <c r="M28">
-        <v>0.00036882729498072513</v>
+        <v>0.00035175900263562272</v>
       </c>
       <c r="N28">
-        <v>8.0825846154021497e-005</v>
+        <v>7.6739270380916588e-005</v>
       </c>
       <c r="O28">
-        <v>0.00091495896124979374</v>
+        <v>0.00088979808235138929</v>
       </c>
       <c r="P28">
-        <v>0.00066126880849868663</v>
+        <v>0.00064891673791304147</v>
       </c>
       <c r="Q28">
-        <v>0.00083193504082763555</v>
+        <v>0.00080616989676829387</v>
       </c>
       <c r="R28">
-        <v>0.0008455155953252969</v>
+        <v>0.00081760394751968063</v>
       </c>
       <c r="S28">
-        <v>0.00023525985564097228</v>
+        <v>0.00023603575976264017</v>
       </c>
       <c r="T28">
-        <v>0.00089916197048965174</v>
+        <v>0.00085620122231748312</v>
       </c>
       <c r="U28">
-        <v>0.0010528781616053484</v>
+        <v>0.0010130821971961975</v>
       </c>
       <c r="V28">
-        <v>0.0010192537959087982</v>
+        <v>0.00097741732400680702</v>
       </c>
       <c r="W28">
-        <v>0.0010235420451779663</v>
+        <v>0.0010001953792593316</v>
       </c>
       <c r="X28">
-        <v>0.0010073955511555699</v>
+        <v>0.00097691360025171578</v>
       </c>
       <c r="Y28">
-        <v>0.0011215713986126171</v>
+        <v>0.0010854516708666087</v>
       </c>
       <c r="Z28">
-        <v>-2.4013365307961102e-005</v>
+        <v>-2.1917991800439777e-005</v>
       </c>
       <c r="AA28">
-        <v>-2.1311338670532576e-005</v>
+        <v>-1.4349466299931699e-005</v>
       </c>
       <c r="AB28">
-        <v>4.5554320765456031e-005</v>
+        <v>3.7629052355877407e-005</v>
       </c>
       <c r="AC28">
-        <v>0.0038709913308441249</v>
+        <v>0.0038026550845294566</v>
       </c>
       <c r="AD28">
-        <v>0.0016605207019725907</v>
+        <v>0.0016076323219412422</v>
       </c>
       <c r="AE28">
-        <v>0.00058780236857896618</v>
+        <v>0.00056155908132599552</v>
       </c>
       <c r="AF28">
-        <v>-0.00033927870204009006</v>
+        <v>-0.00041191019213865777</v>
       </c>
     </row>
     <row r="29">
@@ -3183,97 +3183,97 @@
         <v>41</v>
       </c>
       <c r="B29">
-        <v>-0.18530046037839767</v>
+        <v>-0.20440520498978301</v>
       </c>
       <c r="C29">
-        <v>-0.0004652718649726449</v>
+        <v>-0.00047149176486758614</v>
       </c>
       <c r="D29">
-        <v>0.00023231043834136614</v>
+        <v>0.00025038700768558256</v>
       </c>
       <c r="E29">
-        <v>-5.4639387720562785e-006</v>
+        <v>-5.7861282063362827e-006</v>
       </c>
       <c r="F29">
-        <v>0.00093280133627342884</v>
+        <v>0.00094297749891236304</v>
       </c>
       <c r="G29">
-        <v>0.0010093788417061046</v>
+        <v>0.0009958487500214214</v>
       </c>
       <c r="H29">
-        <v>0.00072591868540034486</v>
+        <v>0.00070980837334838924</v>
       </c>
       <c r="I29">
-        <v>-0.0006662390109181543</v>
+        <v>-0.0006613609584761428</v>
       </c>
       <c r="J29">
-        <v>-0.00041315936917586584</v>
+        <v>-0.00039227205058577595</v>
       </c>
       <c r="K29">
-        <v>-0.00014962454686858178</v>
+        <v>-0.00013283565489415495</v>
       </c>
       <c r="L29">
-        <v>-0.00025962958563299516</v>
+        <v>-0.00030057455987180307</v>
       </c>
       <c r="M29">
-        <v>0.00093441398487588076</v>
+        <v>0.00093745277932571515</v>
       </c>
       <c r="N29">
-        <v>-6.7322789170863942e-005</v>
+        <v>-0.00013411624186865801</v>
       </c>
       <c r="O29">
-        <v>0.0041337960087751528</v>
+        <v>0.0040565538540559797</v>
       </c>
       <c r="P29">
-        <v>0.0037694255432193569</v>
+        <v>0.0037078822696152889</v>
       </c>
       <c r="Q29">
-        <v>0.0038435037820535247</v>
+        <v>0.0037673529644965944</v>
       </c>
       <c r="R29">
-        <v>0.0039129067942044321</v>
+        <v>0.0038455019985996655</v>
       </c>
       <c r="S29">
-        <v>0.0037627366577099464</v>
+        <v>0.0037007543919348007</v>
       </c>
       <c r="T29">
-        <v>0.0035529956773206932</v>
+        <v>0.0034918990804817633</v>
       </c>
       <c r="U29">
-        <v>0.006399662749753449</v>
+        <v>0.0062246576671145734</v>
       </c>
       <c r="V29">
-        <v>0.0041395571462687995</v>
+        <v>0.0040540843389370966</v>
       </c>
       <c r="W29">
-        <v>0.004292028419354707</v>
+        <v>0.004227232044407842</v>
       </c>
       <c r="X29">
-        <v>0.004127985227039224</v>
+        <v>0.0040626064447288196</v>
       </c>
       <c r="Y29">
-        <v>0.004277809101152729</v>
+        <v>0.0041961266474661359</v>
       </c>
       <c r="Z29">
-        <v>0.00016748782875833693</v>
+        <v>0.00016061840862529377</v>
       </c>
       <c r="AA29">
-        <v>-0.00097782986556344811</v>
+        <v>-0.00090025848297930772</v>
       </c>
       <c r="AB29">
-        <v>-0.00087718955161898856</v>
+        <v>-0.00087583067108481063</v>
       </c>
       <c r="AC29">
-        <v>0.0016605207019725907</v>
+        <v>0.0016076323219412422</v>
       </c>
       <c r="AD29">
-        <v>0.022759579619367119</v>
+        <v>0.022148300869664943</v>
       </c>
       <c r="AE29">
-        <v>0.0015152515587682337</v>
+        <v>0.0014730329928058614</v>
       </c>
       <c r="AF29">
-        <v>-0.0098350311484416558</v>
+        <v>-0.0098627648502508259</v>
       </c>
     </row>
     <row r="30">
@@ -3281,97 +3281,97 @@
         <v>42</v>
       </c>
       <c r="B30">
-        <v>-0.18482331179562636</v>
+        <v>-0.20992770628085858</v>
       </c>
       <c r="C30">
-        <v>2.5720529073133588e-006</v>
+        <v>-2.4216010275010592e-005</v>
       </c>
       <c r="D30">
-        <v>2.6690207373225583e-005</v>
+        <v>3.1623440649669902e-005</v>
       </c>
       <c r="E30">
-        <v>-1.0366898333491296e-006</v>
+        <v>-1.0915277513781723e-006</v>
       </c>
       <c r="F30">
-        <v>-0.00021567594819360959</v>
+        <v>-0.00016788434318726515</v>
       </c>
       <c r="G30">
-        <v>-0.00011602191616720341</v>
+        <v>-9.529260626359626e-005</v>
       </c>
       <c r="H30">
-        <v>-0.00011953630469916949</v>
+        <v>-5.4739881428440265e-005</v>
       </c>
       <c r="I30">
-        <v>-3.7175424572115931e-005</v>
+        <v>-5.7073530645228862e-005</v>
       </c>
       <c r="J30">
-        <v>-2.4776596705223001e-005</v>
+        <v>-4.0313732663310058e-005</v>
       </c>
       <c r="K30">
-        <v>-3.0191651593918086e-005</v>
+        <v>-3.678219805361481e-005</v>
       </c>
       <c r="L30">
-        <v>7.8277593571055232e-005</v>
+        <v>6.756641963733196e-005</v>
       </c>
       <c r="M30">
-        <v>0.0002959661078906794</v>
+        <v>0.00028017165294491901</v>
       </c>
       <c r="N30">
-        <v>9.7717856914546685e-005</v>
+        <v>9.9494135433479962e-005</v>
       </c>
       <c r="O30">
-        <v>0.00069584599408913507</v>
+        <v>0.00068659941555398931</v>
       </c>
       <c r="P30">
-        <v>0.00041677762801240771</v>
+        <v>0.00041027442714807431</v>
       </c>
       <c r="Q30">
-        <v>0.00066866753885169749</v>
+        <v>0.00066304719259550286</v>
       </c>
       <c r="R30">
-        <v>0.00056262206897762291</v>
+        <v>0.0005601594128802201</v>
       </c>
       <c r="S30">
-        <v>0.00021752375765130114</v>
+        <v>0.00022952962553594164</v>
       </c>
       <c r="T30">
-        <v>0.0004763512895334504</v>
+        <v>0.00046633034542556748</v>
       </c>
       <c r="U30">
-        <v>0.00070015276382089011</v>
+        <v>0.00069089281090230713</v>
       </c>
       <c r="V30">
-        <v>0.00087271599260421956</v>
+        <v>0.00085145815746772986</v>
       </c>
       <c r="W30">
-        <v>0.0007798203814307819</v>
+        <v>0.000790384155859607</v>
       </c>
       <c r="X30">
-        <v>0.0006491054737402446</v>
+        <v>0.00062913858855751697</v>
       </c>
       <c r="Y30">
-        <v>0.00075300304495632743</v>
+        <v>0.00072922057288449813</v>
       </c>
       <c r="Z30">
-        <v>-3.2374072420371931e-005</v>
+        <v>-3.0810460231410312e-005</v>
       </c>
       <c r="AA30">
-        <v>0.00076269541064717173</v>
+        <v>0.00081312700733148055</v>
       </c>
       <c r="AB30">
-        <v>9.330083940996896e-005</v>
+        <v>5.7965814224204842e-005</v>
       </c>
       <c r="AC30">
-        <v>0.00058780236857896618</v>
+        <v>0.00056155908132599552</v>
       </c>
       <c r="AD30">
-        <v>0.0015152515587682337</v>
+        <v>0.0014730329928058614</v>
       </c>
       <c r="AE30">
-        <v>0.0075807735844450044</v>
+        <v>0.0075885216199941506</v>
       </c>
       <c r="AF30">
-        <v>-0.000389386625744857</v>
+        <v>-0.00047846108826925823</v>
       </c>
     </row>
     <row r="31">
@@ -3379,97 +3379,97 @@
         <v>43</v>
       </c>
       <c r="B31">
-        <v>-3.7629074346571407</v>
+        <v>-3.7898611329164122</v>
       </c>
       <c r="C31">
-        <v>0.00058074083582644251</v>
+        <v>0.00049682436959361416</v>
       </c>
       <c r="D31">
-        <v>-0.016902746872015924</v>
+        <v>-0.017514934000154542</v>
       </c>
       <c r="E31">
-        <v>0.00030605520929484053</v>
+        <v>0.00031826043205515137</v>
       </c>
       <c r="F31">
-        <v>-0.011634867584163894</v>
+        <v>-0.011777815928539704</v>
       </c>
       <c r="G31">
-        <v>-0.0079889883797299027</v>
+        <v>-0.0080302498767641749</v>
       </c>
       <c r="H31">
-        <v>-0.0092651409975657139</v>
+        <v>-0.0093680085557710947</v>
       </c>
       <c r="I31">
-        <v>-0.011543899938597269</v>
+        <v>-0.011643344785943179</v>
       </c>
       <c r="J31">
-        <v>-0.0094594150932819053</v>
+        <v>-0.0098749837216438457</v>
       </c>
       <c r="K31">
-        <v>-0.011901656189561797</v>
+        <v>-0.012062052359739724</v>
       </c>
       <c r="L31">
-        <v>-0.011446684140591565</v>
+        <v>-0.01152302452652448</v>
       </c>
       <c r="M31">
-        <v>-0.0111729166654637</v>
+        <v>-0.011436455466038706</v>
       </c>
       <c r="N31">
-        <v>-0.012635908038859202</v>
+        <v>-0.012853668771424229</v>
       </c>
       <c r="O31">
-        <v>-0.007059224968605015</v>
+        <v>-0.0072514304522253853</v>
       </c>
       <c r="P31">
-        <v>-0.0064443620420500608</v>
+        <v>-0.0064453537719234774</v>
       </c>
       <c r="Q31">
-        <v>-0.0071908079855674207</v>
+        <v>-0.007538787676784591</v>
       </c>
       <c r="R31">
-        <v>-0.0056772332627614917</v>
+        <v>-0.0060338518062252227</v>
       </c>
       <c r="S31">
-        <v>-0.0059732266861116674</v>
+        <v>-0.0060445062227189724</v>
       </c>
       <c r="T31">
-        <v>-0.0065910688546137238</v>
+        <v>-0.0067712057912613201</v>
       </c>
       <c r="U31">
-        <v>-0.0064171610485045929</v>
+        <v>-0.0067438437145954881</v>
       </c>
       <c r="V31">
-        <v>-0.0062129698122974</v>
+        <v>-0.0070156974466466914</v>
       </c>
       <c r="W31">
-        <v>-0.0056687295865195742</v>
+        <v>-0.0060112535132983572</v>
       </c>
       <c r="X31">
-        <v>-0.0089471025665843751</v>
+        <v>-0.0090350103890579937</v>
       </c>
       <c r="Y31">
-        <v>-0.0040503102255273742</v>
+        <v>-0.0042619176919000438</v>
       </c>
       <c r="Z31">
-        <v>-0.00051834020972574475</v>
+        <v>-0.0004969047454233944</v>
       </c>
       <c r="AA31">
-        <v>0.0017880003694124883</v>
+        <v>0.0019630668412878266</v>
       </c>
       <c r="AB31">
-        <v>0.0025096001777446314</v>
+        <v>0.0025807902245204772</v>
       </c>
       <c r="AC31">
-        <v>-0.00033927870204009006</v>
+        <v>-0.00041191019213865777</v>
       </c>
       <c r="AD31">
-        <v>-0.0098350311484416558</v>
+        <v>-0.0098627648502508259</v>
       </c>
       <c r="AE31">
-        <v>-0.000389386625744857</v>
+        <v>-0.00047846108826925823</v>
       </c>
       <c r="AF31">
-        <v>0.25640652059959024</v>
+        <v>0.2640196494617007</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_leave_parental_home.xlsx
+++ b/input/reg_leave_parental_home.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="49">
   <si>
     <t>Description:</t>
   </si>
@@ -168,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -227,6 +227,66 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -236,7 +296,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -286,11 +346,53 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -316,6 +418,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -329,7 +455,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -350,10 +476,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -366,7 +492,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
@@ -388,12 +514,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="12" t="s">
         <v>44</v>
       </c>
     </row>
